--- a/Final data extraction_checked_clean.xlsx
+++ b/Final data extraction_checked_clean.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/vl22683_bristol_ac_uk/Documents/Documents/Misc/UNAIDS/FSW/Analysis/Analysis/Structural-Barriers-FSW-Review/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="8_{57F6CB69-E802-48CB-BC8C-AE55230DF050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{031C352B-CDE7-4FFB-9F39-3CAD66FF01D8}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="8_{57F6CB69-E802-48CB-BC8C-AE55230DF050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F4B40E3-F47C-4936-96F7-9F965F4E384C}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B15207E7-DAAE-40B8-981F-8519D2716002}"/>
   </bookViews>
@@ -59,6 +59,12 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={E7048C25-104E-4675-A95C-E812B6DD6BF4}</author>
+    <author>tc={2F62E598-90C6-4D82-AB67-B976649E5C79}</author>
+    <author>tc={783D4DD9-BAF3-4346-92DB-B69617C5AFF1}</author>
+    <author>tc={08F9D07E-6013-4A64-82E7-E46D2826F100}</author>
+    <author>tc={268C0D53-D6A6-4E59-9995-8C6ED708B105}</author>
+    <author>tc={60996FA8-6F37-421F-B95D-D8A8C1756904}</author>
     <author>tc={6077D12D-0822-4C1B-A082-34FDBDF12D7D}</author>
     <author>tc={914EC8C3-060D-4CAD-AEEA-7C21592D51A2}</author>
     <author>tc={984A2285-FB9F-47C8-9AB5-E3FDB43CBA40}</author>
@@ -98,12 +104,6 @@
     <author>tc={C9B78CB0-D806-48C0-AD9B-84EF2C8A0988}</author>
     <author>tc={D67639CC-A123-41EA-9BF6-0A796AAF68CD}</author>
     <author>tc={1528D086-EBFF-425B-8127-14D43A4FCA75}</author>
-    <author>tc={E7048C25-104E-4675-A95C-E812B6DD6BF4}</author>
-    <author>tc={2F62E598-90C6-4D82-AB67-B976649E5C79}</author>
-    <author>tc={783D4DD9-BAF3-4346-92DB-B69617C5AFF1}</author>
-    <author>tc={08F9D07E-6013-4A64-82E7-E46D2826F100}</author>
-    <author>tc={268C0D53-D6A6-4E59-9995-8C6ED708B105}</author>
-    <author>tc={60996FA8-6F37-421F-B95D-D8A8C1756904}</author>
     <author>tc={B209DF1E-B64C-4C81-A700-7874271C29CF}</author>
     <author>tc={8D8F90F0-9297-401B-A1D6-EEEB81526CF3}</author>
     <author>tc={DEA8A383-C541-4D0B-A78F-12036AAE8512}</author>
@@ -300,337 +300,7 @@
     <author>tc={E3C49439-4CE0-4914-8A05-C197153AB85E}</author>
   </authors>
   <commentList>
-    <comment ref="AB2" authorId="0" shapeId="0" xr:uid="{6077D12D-0822-4C1B-A082-34FDBDF12D7D}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    It should be possible to use the results in tables 2 and 3 to create a variable for “Any violent experiences” which would be more useful than this
-Reply:
-    Table 3 is condom use
-Reply:
-    Table 4 is HIV but when I include it, I get an OR of 31.51. it’s a confusing study. Let’s discuss
-Reply:
-    Spoke to Jack and decided to keep as is because of adjusted ORs</t>
-      </text>
-    </comment>
-    <comment ref="AT12" authorId="1" shapeId="0" xr:uid="{914EC8C3-060D-4CAD-AEEA-7C21592D51A2}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    1.743</t>
-      </text>
-    </comment>
-    <comment ref="AU12" authorId="2" shapeId="0" xr:uid="{984A2285-FB9F-47C8-9AB5-E3FDB43CBA40}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    1.002</t>
-      </text>
-    </comment>
-    <comment ref="AX12" authorId="3" shapeId="0" xr:uid="{36397AA6-56E0-46F1-9B8F-7D52A57FE877}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    1.743</t>
-      </text>
-    </comment>
-    <comment ref="K18" authorId="4" shapeId="0" xr:uid="{FC96265B-1784-4414-A44D-8FF495448F25}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    “Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</t>
-      </text>
-    </comment>
-    <comment ref="L18" authorId="5" shapeId="0" xr:uid="{3FC56194-C8C0-4C5B-9B4F-885AFC6B3104}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    “Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</t>
-      </text>
-    </comment>
-    <comment ref="Y18" authorId="6" shapeId="0" xr:uid="{B4B5594F-3597-4CB9-98BA-2DF7AE10357D}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Back calculate from prevalence?</t>
-      </text>
-    </comment>
-    <comment ref="Z18" authorId="7" shapeId="0" xr:uid="{11FCD21A-07F0-4BD4-B5A8-66F97F50990E}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    0.053? “HIV prevalence was estimated as 5.3% with a 95% confidence interval (CI) (4.4%–6.2%).“</t>
-      </text>
-    </comment>
-    <comment ref="K19" authorId="8" shapeId="0" xr:uid="{238EDB2C-16AF-4812-AD1B-6A07F1561048}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    “Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</t>
-      </text>
-    </comment>
-    <comment ref="L19" authorId="9" shapeId="0" xr:uid="{E9D7F8BB-47CB-4D0B-B77C-B1AB387ABAC0}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    “Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</t>
-      </text>
-    </comment>
-    <comment ref="Y19" authorId="10" shapeId="0" xr:uid="{397E0321-6508-471E-8C40-2D5D16A0D0DD}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Back calculate from prevalence?</t>
-      </text>
-    </comment>
-    <comment ref="Z19" authorId="11" shapeId="0" xr:uid="{586E2BF3-6B79-4E45-9DD6-696F2DA503A8}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    0.053? “HIV prevalence was estimated as 5.3% with a 95% confidence interval (CI) (4.4%–6.2%).“</t>
-      </text>
-    </comment>
-    <comment ref="Z20" authorId="12" shapeId="0" xr:uid="{4C5CBF93-98BA-4F0A-A373-2ABD7A4802AE}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    I could only see “The adjusted prevalence of HIV was 3.2% (95% CI 1.76–5.75).“
-Reply:
-    Table 1 shows 72 hiv+. Ask Jack whether we use adjusted or unadjusted</t>
-      </text>
-    </comment>
-    <comment ref="Z21" authorId="13" shapeId="0" xr:uid="{EAC91F3F-7C39-46E7-A671-022EE9C432E8}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    I could only see “The adjusted prevalence of HIV was 3.2% (95% CI 1.76–5.75).“</t>
-      </text>
-    </comment>
-    <comment ref="A22" authorId="14" shapeId="0" xr:uid="{83CC3671-6338-4CD1-ABD8-4C9EC9003E41}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    2019</t>
-      </text>
-    </comment>
-    <comment ref="D22" authorId="15" shapeId="0" xr:uid="{0E867546-6B89-4EFC-B072-7637D2BE57A1}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    2019</t>
-      </text>
-    </comment>
-    <comment ref="A23" authorId="16" shapeId="0" xr:uid="{F62C4C7A-B342-40B1-A7EC-4AF2916C68F8}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    2019</t>
-      </text>
-    </comment>
-    <comment ref="D23" authorId="17" shapeId="0" xr:uid="{C11FE7A7-D031-49C0-ADEC-B47D7669289D}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    2019</t>
-      </text>
-    </comment>
-    <comment ref="AG24" authorId="18" shapeId="0" xr:uid="{B340D370-DD42-45C2-99F1-F392C636C507}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    These are the number with outcome?
-Reply:
-    Not right</t>
-      </text>
-    </comment>
-    <comment ref="AH24" authorId="19" shapeId="0" xr:uid="{8F037DF1-D3F6-4675-B321-9444B3086129}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    If this is what you are using when pooling then 60.4%</t>
-      </text>
-    </comment>
-    <comment ref="AO24" authorId="20" shapeId="0" xr:uid="{16B3F7F6-45FC-4058-87A4-8C65D2C81A62}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Self-report being HIV+
-Reply:
-    Does that meet inclusion criteria??</t>
-      </text>
-    </comment>
-    <comment ref="AX24" authorId="21" shapeId="0" xr:uid="{39113FCF-CD56-4E26-92B6-BE77DCA66775}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    I think you cn work this out: 0.59 (0.20-1.72)</t>
-      </text>
-    </comment>
-    <comment ref="AG25" authorId="22" shapeId="0" xr:uid="{A9D7F15F-BE27-46D2-AD8B-80D032ABAF56}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    These are the number with outcome?
-Reply:
-    Not right</t>
-      </text>
-    </comment>
-    <comment ref="AH25" authorId="23" shapeId="0" xr:uid="{259EC1F6-3229-4043-BBD1-D170A8630285}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    If this is what you are using when pooling then 60.4%</t>
-      </text>
-    </comment>
-    <comment ref="AO25" authorId="24" shapeId="0" xr:uid="{DFFEADBE-C45A-440E-ACB5-5C739F26F7FD}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Self report HIV negative</t>
-      </text>
-    </comment>
-    <comment ref="AX25" authorId="25" shapeId="0" xr:uid="{77278C7A-E665-495E-9F77-ECFB90597AB7}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    I think you can work this out: 0.83 (0.66-1.05)
-Reply:
-    Well done</t>
-      </text>
-    </comment>
-    <comment ref="L30" authorId="26" shapeId="0" xr:uid="{CC904001-032B-4B72-B329-5D6E2173ADEE}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    937</t>
-      </text>
-    </comment>
-    <comment ref="L31" authorId="27" shapeId="0" xr:uid="{A74F3F70-F7D7-48F9-A871-46F055A588F2}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    740</t>
-      </text>
-    </comment>
-    <comment ref="L32" authorId="28" shapeId="0" xr:uid="{789FF504-3E8E-486F-97E3-8B97C7BDF7CD}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    937</t>
-      </text>
-    </comment>
-    <comment ref="L34" authorId="29" shapeId="0" xr:uid="{F9CD37FE-3B73-48E9-8D33-F153AB42EC13}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    735</t>
-      </text>
-    </comment>
-    <comment ref="L35" authorId="30" shapeId="0" xr:uid="{FAD2C12C-D163-4465-B27A-15F1F4A037DF}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    735</t>
-      </text>
-    </comment>
-    <comment ref="L36" authorId="31" shapeId="0" xr:uid="{82578D19-7394-4157-8AD4-0B3777DC7B48}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    937</t>
-      </text>
-    </comment>
-    <comment ref="L37" authorId="32" shapeId="0" xr:uid="{02D548A8-CEC1-42B7-8CC9-BFF35A1AEEF0}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    739</t>
-      </text>
-    </comment>
-    <comment ref="L38" authorId="33" shapeId="0" xr:uid="{AE0B9FF2-A8F9-44EE-96BF-A77B61D12DA8}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    453 “Living with HIV” table 4</t>
-      </text>
-    </comment>
-    <comment ref="BC38" authorId="34" shapeId="0" xr:uid="{34CB3925-8D93-473E-AE72-BB45AB11435B}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Not useable, HIV was not outcome in adjusted model.
-Reply:
-    ok</t>
-      </text>
-    </comment>
-    <comment ref="L39" authorId="35" shapeId="0" xr:uid="{6B0D38DB-8812-4147-8FA9-F01465132932}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    453 “Living with HIV” table 4</t>
-      </text>
-    </comment>
-    <comment ref="L40" authorId="36" shapeId="0" xr:uid="{C9B78CB0-D806-48C0-AD9B-84EF2C8A0988}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    462 “Ever tested for HIV” table 4</t>
-      </text>
-    </comment>
-    <comment ref="L41" authorId="37" shapeId="0" xr:uid="{D67639CC-A123-41EA-9BF6-0A796AAF68CD}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    462 “Ever tested for HIV” table 4</t>
-      </text>
-    </comment>
-    <comment ref="BG42" authorId="38" shapeId="0" xr:uid="{1528D086-EBFF-425B-8127-14D43A4FCA75}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Alcohol use, STIs, type of sexual intercourse</t>
-      </text>
-    </comment>
-    <comment ref="A44" authorId="39" shapeId="0" xr:uid="{E7048C25-104E-4675-A95C-E812B6DD6BF4}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{E7048C25-104E-4675-A95C-E812B6DD6BF4}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -640,7 +310,7 @@
     Strange this study isnt in the MSM/TGW review</t>
       </text>
     </comment>
-    <comment ref="X44" authorId="40" shapeId="0" xr:uid="{2F62E598-90C6-4D82-AB67-B976649E5C79}">
+    <comment ref="X2" authorId="1" shapeId="0" xr:uid="{2F62E598-90C6-4D82-AB67-B976649E5C79}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -648,7 +318,7 @@
     0.7424</t>
       </text>
     </comment>
-    <comment ref="AB44" authorId="41" shapeId="0" xr:uid="{783D4DD9-BAF3-4346-92DB-B69617C5AFF1}">
+    <comment ref="AB2" authorId="2" shapeId="0" xr:uid="{783D4DD9-BAF3-4346-92DB-B69617C5AFF1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -663,7 +333,7 @@
     Beaten or raped in past year</t>
       </text>
     </comment>
-    <comment ref="AC44" authorId="42" shapeId="0" xr:uid="{08F9D07E-6013-4A64-82E7-E46D2826F100}">
+    <comment ref="AC2" authorId="3" shapeId="0" xr:uid="{08F9D07E-6013-4A64-82E7-E46D2826F100}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -678,7 +348,7 @@
     Beaten/raped in past year</t>
       </text>
     </comment>
-    <comment ref="AU44" authorId="43" shapeId="0" xr:uid="{268C0D53-D6A6-4E59-9995-8C6ED708B105}">
+    <comment ref="AU2" authorId="4" shapeId="0" xr:uid="{268C0D53-D6A6-4E59-9995-8C6ED708B105}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -687,12 +357,342 @@
 </t>
       </text>
     </comment>
-    <comment ref="AV44" authorId="44" shapeId="0" xr:uid="{60996FA8-6F37-421F-B95D-D8A8C1756904}">
+    <comment ref="AV2" authorId="5" shapeId="0" xr:uid="{60996FA8-6F37-421F-B95D-D8A8C1756904}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     8.388</t>
+      </text>
+    </comment>
+    <comment ref="AB3" authorId="6" shapeId="0" xr:uid="{6077D12D-0822-4C1B-A082-34FDBDF12D7D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    It should be possible to use the results in tables 2 and 3 to create a variable for “Any violent experiences” which would be more useful than this
+Reply:
+    Table 3 is condom use
+Reply:
+    Table 4 is HIV but when I include it, I get an OR of 31.51. it’s a confusing study. Let’s discuss
+Reply:
+    Spoke to Jack and decided to keep as is because of adjusted ORs</t>
+      </text>
+    </comment>
+    <comment ref="AT13" authorId="7" shapeId="0" xr:uid="{914EC8C3-060D-4CAD-AEEA-7C21592D51A2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    1.743</t>
+      </text>
+    </comment>
+    <comment ref="AU13" authorId="8" shapeId="0" xr:uid="{984A2285-FB9F-47C8-9AB5-E3FDB43CBA40}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    1.002</t>
+      </text>
+    </comment>
+    <comment ref="AX13" authorId="9" shapeId="0" xr:uid="{36397AA6-56E0-46F1-9B8F-7D52A57FE877}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    1.743</t>
+      </text>
+    </comment>
+    <comment ref="K19" authorId="10" shapeId="0" xr:uid="{FC96265B-1784-4414-A44D-8FF495448F25}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    “Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</t>
+      </text>
+    </comment>
+    <comment ref="L19" authorId="11" shapeId="0" xr:uid="{3FC56194-C8C0-4C5B-9B4F-885AFC6B3104}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    “Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</t>
+      </text>
+    </comment>
+    <comment ref="Y19" authorId="12" shapeId="0" xr:uid="{B4B5594F-3597-4CB9-98BA-2DF7AE10357D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Back calculate from prevalence?</t>
+      </text>
+    </comment>
+    <comment ref="Z19" authorId="13" shapeId="0" xr:uid="{11FCD21A-07F0-4BD4-B5A8-66F97F50990E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    0.053? “HIV prevalence was estimated as 5.3% with a 95% confidence interval (CI) (4.4%–6.2%).“</t>
+      </text>
+    </comment>
+    <comment ref="K20" authorId="14" shapeId="0" xr:uid="{238EDB2C-16AF-4812-AD1B-6A07F1561048}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    “Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</t>
+      </text>
+    </comment>
+    <comment ref="L20" authorId="15" shapeId="0" xr:uid="{E9D7F8BB-47CB-4D0B-B77C-B1AB387ABAC0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    “Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</t>
+      </text>
+    </comment>
+    <comment ref="Y20" authorId="16" shapeId="0" xr:uid="{397E0321-6508-471E-8C40-2D5D16A0D0DD}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Back calculate from prevalence?</t>
+      </text>
+    </comment>
+    <comment ref="Z20" authorId="17" shapeId="0" xr:uid="{586E2BF3-6B79-4E45-9DD6-696F2DA503A8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    0.053? “HIV prevalence was estimated as 5.3% with a 95% confidence interval (CI) (4.4%–6.2%).“</t>
+      </text>
+    </comment>
+    <comment ref="Z21" authorId="18" shapeId="0" xr:uid="{4C5CBF93-98BA-4F0A-A373-2ABD7A4802AE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I could only see “The adjusted prevalence of HIV was 3.2% (95% CI 1.76–5.75).“
+Reply:
+    Table 1 shows 72 hiv+. Ask Jack whether we use adjusted or unadjusted</t>
+      </text>
+    </comment>
+    <comment ref="Z22" authorId="19" shapeId="0" xr:uid="{EAC91F3F-7C39-46E7-A671-022EE9C432E8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I could only see “The adjusted prevalence of HIV was 3.2% (95% CI 1.76–5.75).“</t>
+      </text>
+    </comment>
+    <comment ref="A23" authorId="20" shapeId="0" xr:uid="{83CC3671-6338-4CD1-ABD8-4C9EC9003E41}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    2019</t>
+      </text>
+    </comment>
+    <comment ref="D23" authorId="21" shapeId="0" xr:uid="{0E867546-6B89-4EFC-B072-7637D2BE57A1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    2019</t>
+      </text>
+    </comment>
+    <comment ref="A24" authorId="22" shapeId="0" xr:uid="{F62C4C7A-B342-40B1-A7EC-4AF2916C68F8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    2019</t>
+      </text>
+    </comment>
+    <comment ref="D24" authorId="23" shapeId="0" xr:uid="{C11FE7A7-D031-49C0-ADEC-B47D7669289D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    2019</t>
+      </text>
+    </comment>
+    <comment ref="AG25" authorId="24" shapeId="0" xr:uid="{B340D370-DD42-45C2-99F1-F392C636C507}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    These are the number with outcome?
+Reply:
+    Not right</t>
+      </text>
+    </comment>
+    <comment ref="AH25" authorId="25" shapeId="0" xr:uid="{8F037DF1-D3F6-4675-B321-9444B3086129}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    If this is what you are using when pooling then 60.4%</t>
+      </text>
+    </comment>
+    <comment ref="AO25" authorId="26" shapeId="0" xr:uid="{16B3F7F6-45FC-4058-87A4-8C65D2C81A62}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Self-report being HIV+
+Reply:
+    Does that meet inclusion criteria??</t>
+      </text>
+    </comment>
+    <comment ref="AX25" authorId="27" shapeId="0" xr:uid="{39113FCF-CD56-4E26-92B6-BE77DCA66775}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I think you cn work this out: 0.59 (0.20-1.72)</t>
+      </text>
+    </comment>
+    <comment ref="AG26" authorId="28" shapeId="0" xr:uid="{A9D7F15F-BE27-46D2-AD8B-80D032ABAF56}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    These are the number with outcome?
+Reply:
+    Not right</t>
+      </text>
+    </comment>
+    <comment ref="AH26" authorId="29" shapeId="0" xr:uid="{259EC1F6-3229-4043-BBD1-D170A8630285}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    If this is what you are using when pooling then 60.4%</t>
+      </text>
+    </comment>
+    <comment ref="AO26" authorId="30" shapeId="0" xr:uid="{DFFEADBE-C45A-440E-ACB5-5C739F26F7FD}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Self report HIV negative</t>
+      </text>
+    </comment>
+    <comment ref="AX26" authorId="31" shapeId="0" xr:uid="{77278C7A-E665-495E-9F77-ECFB90597AB7}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I think you can work this out: 0.83 (0.66-1.05)
+Reply:
+    Well done</t>
+      </text>
+    </comment>
+    <comment ref="L31" authorId="32" shapeId="0" xr:uid="{CC904001-032B-4B72-B329-5D6E2173ADEE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    937</t>
+      </text>
+    </comment>
+    <comment ref="L32" authorId="33" shapeId="0" xr:uid="{A74F3F70-F7D7-48F9-A871-46F055A588F2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    740</t>
+      </text>
+    </comment>
+    <comment ref="L33" authorId="34" shapeId="0" xr:uid="{789FF504-3E8E-486F-97E3-8B97C7BDF7CD}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    937</t>
+      </text>
+    </comment>
+    <comment ref="L35" authorId="35" shapeId="0" xr:uid="{F9CD37FE-3B73-48E9-8D33-F153AB42EC13}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    735</t>
+      </text>
+    </comment>
+    <comment ref="L36" authorId="36" shapeId="0" xr:uid="{FAD2C12C-D163-4465-B27A-15F1F4A037DF}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    735</t>
+      </text>
+    </comment>
+    <comment ref="L37" authorId="37" shapeId="0" xr:uid="{82578D19-7394-4157-8AD4-0B3777DC7B48}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    937</t>
+      </text>
+    </comment>
+    <comment ref="L38" authorId="38" shapeId="0" xr:uid="{02D548A8-CEC1-42B7-8CC9-BFF35A1AEEF0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    739</t>
+      </text>
+    </comment>
+    <comment ref="L39" authorId="39" shapeId="0" xr:uid="{AE0B9FF2-A8F9-44EE-96BF-A77B61D12DA8}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    453 “Living with HIV” table 4</t>
+      </text>
+    </comment>
+    <comment ref="BC39" authorId="40" shapeId="0" xr:uid="{34CB3925-8D93-473E-AE72-BB45AB11435B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Not useable, HIV was not outcome in adjusted model.
+Reply:
+    ok</t>
+      </text>
+    </comment>
+    <comment ref="L40" authorId="41" shapeId="0" xr:uid="{6B0D38DB-8812-4147-8FA9-F01465132932}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    453 “Living with HIV” table 4</t>
+      </text>
+    </comment>
+    <comment ref="L41" authorId="42" shapeId="0" xr:uid="{C9B78CB0-D806-48C0-AD9B-84EF2C8A0988}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    462 “Ever tested for HIV” table 4</t>
+      </text>
+    </comment>
+    <comment ref="L42" authorId="43" shapeId="0" xr:uid="{D67639CC-A123-41EA-9BF6-0A796AAF68CD}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    462 “Ever tested for HIV” table 4</t>
+      </text>
+    </comment>
+    <comment ref="BG43" authorId="44" shapeId="0" xr:uid="{1528D086-EBFF-425B-8127-14D43A4FCA75}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Alcohol use, STIs, type of sexual intercourse</t>
       </text>
     </comment>
     <comment ref="A45" authorId="45" shapeId="0" xr:uid="{B209DF1E-B64C-4C81-A700-7874271C29CF}">
@@ -8009,9 +8009,6 @@
   </cellStyles>
   <dxfs count="140">
     <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -9109,6 +9106,9 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -9291,7 +9291,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EF64AA3-9CFA-4117-8F6C-A92D23DCFF59}" name="Table1" displayName="Table1" ref="A1:BG227" totalsRowShown="0" headerRowDxfId="139" dataDxfId="138">
   <autoFilter ref="A1:BG227" xr:uid="{70179EDD-82C2-49C7-80B9-689E0A41FA4C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BG227">
-    <sortCondition ref="N1:N227"/>
+    <sortCondition ref="X1:X227"/>
   </sortState>
   <tableColumns count="59">
     <tableColumn id="1" xr3:uid="{658C57FA-92E2-447A-B1B5-40CBA81D2DF3}" name="study" dataDxfId="137"/>
@@ -9309,150 +9309,150 @@
     <tableColumn id="10" xr3:uid="{FEA54EB8-1299-4A79-9C5C-049E1C1986E2}" name="recruitment" dataDxfId="125"/>
     <tableColumn id="11" xr3:uid="{CB762A89-BD25-4282-85F1-6C1C86AB79B2}" name="country" dataDxfId="124"/>
     <tableColumn id="12" xr3:uid="{8A8F6888-EA0A-4BCA-BF8F-DE218F9BB257}" name="cities" dataDxfId="123"/>
-    <tableColumn id="21" xr3:uid="{04675D87-7A4C-45D9-BBF1-D90C7E960FA6}" name="income_cat" dataDxfId="0"/>
-    <tableColumn id="13" xr3:uid="{D33D572A-AA7A-4DF7-87FB-7C164C8FC372}" name="whoregion" dataDxfId="122"/>
-    <tableColumn id="18" xr3:uid="{C8CDC967-FEB9-4C03-9504-3E3175803C6D}" name="representative" dataDxfId="121"/>
-    <tableColumn id="19" xr3:uid="{FE70BEFB-D75C-42A6-8C7B-22EFF1D89FE8}" name="adjust" dataDxfId="120"/>
-    <tableColumn id="15" xr3:uid="{C26B168D-E82D-4276-B98F-51464C701424}" name="design" dataDxfId="119"/>
-    <tableColumn id="14" xr3:uid="{976BB9B8-5854-4385-8BA2-CB722A03FBAB}" name="rob_score_3cat" dataDxfId="118"/>
-    <tableColumn id="22" xr3:uid="{1BDB9EF8-89D1-45E5-A1B8-7DB870B80617}" name="sw_time_frame" dataDxfId="117"/>
-    <tableColumn id="20" xr3:uid="{A2E95678-2690-484E-9D12-A95EBFC7FD9B}" name="sw_time_frame_bin" dataDxfId="116"/>
-    <tableColumn id="23" xr3:uid="{EBF03193-0D58-4EB2-BFF8-E9D8ECE29919}" name="fsw_prop" dataDxfId="115"/>
-    <tableColumn id="24" xr3:uid="{96B2BCC4-3BF2-4F3F-A97F-6EE4BBC0B6EC}" name="hiv_num" dataDxfId="114"/>
-    <tableColumn id="25" xr3:uid="{23C179A1-A93D-4E52-97AF-064983C6E8F8}" name="hiv_perc" dataDxfId="113"/>
-    <tableColumn id="26" xr3:uid="{751B680B-11CE-4898-9C16-4B41E47D3E39}" name="exposure_type" dataDxfId="112"/>
-    <tableColumn id="27" xr3:uid="{609E94CC-0217-4CC2-910B-A627DABA3257}" name="exposure_definition" dataDxfId="111"/>
-    <tableColumn id="28" xr3:uid="{857D044D-425F-4250-84C7-2CEDA57F4C7D}" name="exposure_definition_short" dataDxfId="110"/>
-    <tableColumn id="29" xr3:uid="{00C95CFD-0D7E-4A1D-BD44-8C83C5EA7A1E}" name="exposure_time_frame" dataDxfId="109"/>
-    <tableColumn id="30" xr3:uid="{2197A12C-24F5-407F-935E-35C69DBB248F}" name="exposure_tf_bin" dataDxfId="108"/>
-    <tableColumn id="31" xr3:uid="{3A59D8A9-5A8E-4DFA-9FAC-E4142E66F5D0}" name="perpetrator" dataDxfId="107"/>
-    <tableColumn id="32" xr3:uid="{CDC904E2-A782-4B5F-8713-D08D76DD1EA1}" name="exposed_num" dataDxfId="106"/>
-    <tableColumn id="33" xr3:uid="{5EE2154D-87AC-45E0-9B9A-1218E6B48149}" name="exposed_perc" dataDxfId="105"/>
-    <tableColumn id="85" xr3:uid="{46F0A7EF-CC9F-4BCA-9387-D6AE664F975D}" name="use_exposed" dataDxfId="104"/>
-    <tableColumn id="34" xr3:uid="{3C2B7382-2B65-49B8-9917-F09FD3BBA4D3}" name="outcome" dataDxfId="103"/>
-    <tableColumn id="35" xr3:uid="{A5D8817B-270F-4C4A-9BE7-081DDE2289D0}" name="outcome_definition" dataDxfId="102"/>
-    <tableColumn id="81" xr3:uid="{8DFEE5C3-2CEA-4B32-869E-CFCC47BA808A}" name="outcome_bin" dataDxfId="101"/>
-    <tableColumn id="82" xr3:uid="{A5E87A68-2298-42A9-AD75-B1C372AE896E}" name="outcome_definition_short" dataDxfId="100"/>
-    <tableColumn id="83" xr3:uid="{AF46B98F-F432-4104-8367-E01850DC36F5}" name="current" dataDxfId="99"/>
-    <tableColumn id="84" xr3:uid="{B604FD79-E105-4129-ADCB-1BEAD4822FE6}" name="outcome_denominator" dataDxfId="98"/>
-    <tableColumn id="36" xr3:uid="{267D7E85-B6D2-4F57-85E9-A339D7E0E786}" name="outcome_time_frame" dataDxfId="97"/>
-    <tableColumn id="37" xr3:uid="{47947888-5AAC-43BD-8D66-790EAAE871FE}" name="outcome_tf_bin" dataDxfId="96"/>
-    <tableColumn id="38" xr3:uid="{9A36903C-2E11-45AA-ABF0-D2D04ECDE3F2}" name="adj" dataDxfId="95"/>
-    <tableColumn id="39" xr3:uid="{8A25BFBE-D7F3-4087-A6C6-7A661DB58FF2}" name="effect_best_model" dataDxfId="94"/>
-    <tableColumn id="40" xr3:uid="{792A7E71-9305-4ED7-9F59-267C095A534A}" name="effect_best" dataDxfId="93"/>
-    <tableColumn id="41" xr3:uid="{2DD67F51-EE12-4B29-AC57-0E4BE1990B2D}" name="effect_best_lower" dataDxfId="92"/>
-    <tableColumn id="42" xr3:uid="{BE987A5E-855E-4B52-97C9-59E5FB12D881}" name="effect_best_upper" dataDxfId="91"/>
-    <tableColumn id="43" xr3:uid="{091D6D28-0DC3-4005-8725-ADE93EAB8039}" name="una_effect" dataDxfId="90"/>
-    <tableColumn id="44" xr3:uid="{60377EA6-29C8-4DFC-9077-9153D8C41499}" name="unadj_est" dataDxfId="89"/>
-    <tableColumn id="45" xr3:uid="{3E1B8AE8-EF20-431D-8407-A120395BAD9F}" name="un_lower" dataDxfId="88"/>
-    <tableColumn id="46" xr3:uid="{D007A437-FB60-4E84-87F7-A0F4263F65EE}" name="un_upper" dataDxfId="87"/>
-    <tableColumn id="47" xr3:uid="{0C5D81D3-C5DB-4594-82F2-35EDF2BF9BFA}" name="un_p_val" dataDxfId="86"/>
-    <tableColumn id="48" xr3:uid="{54755E1F-5A90-422E-A3EA-954C502669FB}" name="adj_effect" dataDxfId="85"/>
-    <tableColumn id="49" xr3:uid="{0CAA6F5A-C3DE-45F4-8EB3-FCB2A8BD49A7}" name="adj_est" dataDxfId="84"/>
-    <tableColumn id="50" xr3:uid="{7045C36F-8118-4C05-9A2F-3C77D27CCF93}" name="adj_lower" dataDxfId="83"/>
-    <tableColumn id="51" xr3:uid="{4D52767F-2E64-4EA6-AB5D-8170C66917D6}" name="adj_upper" dataDxfId="82"/>
-    <tableColumn id="52" xr3:uid="{073C2224-2683-477C-AF51-B3E602D3C746}" name="adj_p_val" dataDxfId="81"/>
-    <tableColumn id="53" xr3:uid="{E478DD1C-FB10-458E-8165-DD4CAA4313A7}" name="adjusted_for" dataDxfId="80"/>
+    <tableColumn id="21" xr3:uid="{04675D87-7A4C-45D9-BBF1-D90C7E960FA6}" name="income_cat" dataDxfId="122"/>
+    <tableColumn id="13" xr3:uid="{D33D572A-AA7A-4DF7-87FB-7C164C8FC372}" name="whoregion" dataDxfId="121"/>
+    <tableColumn id="18" xr3:uid="{C8CDC967-FEB9-4C03-9504-3E3175803C6D}" name="representative" dataDxfId="120"/>
+    <tableColumn id="19" xr3:uid="{FE70BEFB-D75C-42A6-8C7B-22EFF1D89FE8}" name="adjust" dataDxfId="119"/>
+    <tableColumn id="15" xr3:uid="{C26B168D-E82D-4276-B98F-51464C701424}" name="design" dataDxfId="118"/>
+    <tableColumn id="14" xr3:uid="{976BB9B8-5854-4385-8BA2-CB722A03FBAB}" name="rob_score_3cat" dataDxfId="117"/>
+    <tableColumn id="22" xr3:uid="{1BDB9EF8-89D1-45E5-A1B8-7DB870B80617}" name="sw_time_frame" dataDxfId="116"/>
+    <tableColumn id="20" xr3:uid="{A2E95678-2690-484E-9D12-A95EBFC7FD9B}" name="sw_time_frame_bin" dataDxfId="115"/>
+    <tableColumn id="23" xr3:uid="{EBF03193-0D58-4EB2-BFF8-E9D8ECE29919}" name="fsw_prop" dataDxfId="114"/>
+    <tableColumn id="24" xr3:uid="{96B2BCC4-3BF2-4F3F-A97F-6EE4BBC0B6EC}" name="hiv_num" dataDxfId="113"/>
+    <tableColumn id="25" xr3:uid="{23C179A1-A93D-4E52-97AF-064983C6E8F8}" name="hiv_perc" dataDxfId="112"/>
+    <tableColumn id="26" xr3:uid="{751B680B-11CE-4898-9C16-4B41E47D3E39}" name="exposure_type" dataDxfId="111"/>
+    <tableColumn id="27" xr3:uid="{609E94CC-0217-4CC2-910B-A627DABA3257}" name="exposure_definition" dataDxfId="110"/>
+    <tableColumn id="28" xr3:uid="{857D044D-425F-4250-84C7-2CEDA57F4C7D}" name="exposure_definition_short" dataDxfId="109"/>
+    <tableColumn id="29" xr3:uid="{00C95CFD-0D7E-4A1D-BD44-8C83C5EA7A1E}" name="exposure_time_frame" dataDxfId="108"/>
+    <tableColumn id="30" xr3:uid="{2197A12C-24F5-407F-935E-35C69DBB248F}" name="exposure_tf_bin" dataDxfId="107"/>
+    <tableColumn id="31" xr3:uid="{3A59D8A9-5A8E-4DFA-9FAC-E4142E66F5D0}" name="perpetrator" dataDxfId="106"/>
+    <tableColumn id="32" xr3:uid="{CDC904E2-A782-4B5F-8713-D08D76DD1EA1}" name="exposed_num" dataDxfId="105"/>
+    <tableColumn id="33" xr3:uid="{5EE2154D-87AC-45E0-9B9A-1218E6B48149}" name="exposed_perc" dataDxfId="104"/>
+    <tableColumn id="85" xr3:uid="{46F0A7EF-CC9F-4BCA-9387-D6AE664F975D}" name="use_exposed" dataDxfId="103"/>
+    <tableColumn id="34" xr3:uid="{3C2B7382-2B65-49B8-9917-F09FD3BBA4D3}" name="outcome" dataDxfId="102"/>
+    <tableColumn id="35" xr3:uid="{A5D8817B-270F-4C4A-9BE7-081DDE2289D0}" name="outcome_definition" dataDxfId="101"/>
+    <tableColumn id="81" xr3:uid="{8DFEE5C3-2CEA-4B32-869E-CFCC47BA808A}" name="outcome_bin" dataDxfId="100"/>
+    <tableColumn id="82" xr3:uid="{A5E87A68-2298-42A9-AD75-B1C372AE896E}" name="outcome_definition_short" dataDxfId="99"/>
+    <tableColumn id="83" xr3:uid="{AF46B98F-F432-4104-8367-E01850DC36F5}" name="current" dataDxfId="98"/>
+    <tableColumn id="84" xr3:uid="{B604FD79-E105-4129-ADCB-1BEAD4822FE6}" name="outcome_denominator" dataDxfId="97"/>
+    <tableColumn id="36" xr3:uid="{267D7E85-B6D2-4F57-85E9-A339D7E0E786}" name="outcome_time_frame" dataDxfId="96"/>
+    <tableColumn id="37" xr3:uid="{47947888-5AAC-43BD-8D66-790EAAE871FE}" name="outcome_tf_bin" dataDxfId="95"/>
+    <tableColumn id="38" xr3:uid="{9A36903C-2E11-45AA-ABF0-D2D04ECDE3F2}" name="adj" dataDxfId="94"/>
+    <tableColumn id="39" xr3:uid="{8A25BFBE-D7F3-4087-A6C6-7A661DB58FF2}" name="effect_best_model" dataDxfId="93"/>
+    <tableColumn id="40" xr3:uid="{792A7E71-9305-4ED7-9F59-267C095A534A}" name="effect_best" dataDxfId="92"/>
+    <tableColumn id="41" xr3:uid="{2DD67F51-EE12-4B29-AC57-0E4BE1990B2D}" name="effect_best_lower" dataDxfId="91"/>
+    <tableColumn id="42" xr3:uid="{BE987A5E-855E-4B52-97C9-59E5FB12D881}" name="effect_best_upper" dataDxfId="90"/>
+    <tableColumn id="43" xr3:uid="{091D6D28-0DC3-4005-8725-ADE93EAB8039}" name="una_effect" dataDxfId="89"/>
+    <tableColumn id="44" xr3:uid="{60377EA6-29C8-4DFC-9077-9153D8C41499}" name="unadj_est" dataDxfId="88"/>
+    <tableColumn id="45" xr3:uid="{3E1B8AE8-EF20-431D-8407-A120395BAD9F}" name="un_lower" dataDxfId="87"/>
+    <tableColumn id="46" xr3:uid="{D007A437-FB60-4E84-87F7-A0F4263F65EE}" name="un_upper" dataDxfId="86"/>
+    <tableColumn id="47" xr3:uid="{0C5D81D3-C5DB-4594-82F2-35EDF2BF9BFA}" name="un_p_val" dataDxfId="85"/>
+    <tableColumn id="48" xr3:uid="{54755E1F-5A90-422E-A3EA-954C502669FB}" name="adj_effect" dataDxfId="84"/>
+    <tableColumn id="49" xr3:uid="{0CAA6F5A-C3DE-45F4-8EB3-FCB2A8BD49A7}" name="adj_est" dataDxfId="83"/>
+    <tableColumn id="50" xr3:uid="{7045C36F-8118-4C05-9A2F-3C77D27CCF93}" name="adj_lower" dataDxfId="82"/>
+    <tableColumn id="51" xr3:uid="{4D52767F-2E64-4EA6-AB5D-8170C66917D6}" name="adj_upper" dataDxfId="81"/>
+    <tableColumn id="52" xr3:uid="{073C2224-2683-477C-AF51-B3E602D3C746}" name="adj_p_val" dataDxfId="80"/>
+    <tableColumn id="53" xr3:uid="{E478DD1C-FB10-458E-8165-DD4CAA4313A7}" name="adjusted_for" dataDxfId="79"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C0514DDE-E88B-4985-B36B-CBE373A28FBD}" name="Table14" displayName="Table14" ref="A1:BE7" totalsRowShown="0" headerRowDxfId="79" dataDxfId="78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C0514DDE-E88B-4985-B36B-CBE373A28FBD}" name="Table14" displayName="Table14" ref="A1:BE7" totalsRowShown="0" headerRowDxfId="78" dataDxfId="77">
   <autoFilter ref="A1:BE7" xr:uid="{70179EDD-82C2-49C7-80B9-689E0A41FA4C}"/>
   <tableColumns count="57">
-    <tableColumn id="1" xr3:uid="{63BDA606-9089-4874-B591-0807542982B0}" name="study" dataDxfId="77"/>
-    <tableColumn id="2" xr3:uid="{4AA8E6CE-2FAC-4107-B8DC-6C83DCBCB093}" name="title" dataDxfId="76"/>
-    <tableColumn id="3" xr3:uid="{14CAD349-3AE5-4AAE-B62E-AB16344DCD7A}" name="author" dataDxfId="75"/>
-    <tableColumn id="4" xr3:uid="{8E5BD801-3765-44D8-9626-6C5BDF351F18}" name="year" dataDxfId="74"/>
-    <tableColumn id="5" xr3:uid="{81893C14-3975-4E03-80A3-DE30289BF32A}" name="pre_2016" dataDxfId="73"/>
-    <tableColumn id="86" xr3:uid="{3885C3B9-A9A0-4B9E-9BFD-8F101CACF3DE}" name="pre2017" dataDxfId="72"/>
-    <tableColumn id="17" xr3:uid="{322147C7-85C6-4C86-A8E1-DC3ADD324E36}" name="rayyan" dataDxfId="71"/>
-    <tableColumn id="6" xr3:uid="{FFBFAFB5-D941-4514-8EA1-91C9AAF90EBD}" name="pub_type" dataDxfId="70"/>
-    <tableColumn id="7" xr3:uid="{69E1E0B1-F32D-4F7A-A87A-9A5482EA93C4}" name="study_design" dataDxfId="69"/>
-    <tableColumn id="8" xr3:uid="{75FFCE04-2838-42F3-B6A4-F84704B19B2A}" name="study_setting" dataDxfId="68"/>
-    <tableColumn id="16" xr3:uid="{56FD4B42-21B3-4295-B6F9-3507E9D803B6}" name="overall_sample_size" dataDxfId="67"/>
-    <tableColumn id="9" xr3:uid="{35FF46C8-B4AA-4BA5-BDA2-9A64E443ED8B}" name="analytical_sample_size" dataDxfId="66"/>
-    <tableColumn id="10" xr3:uid="{4B153F2C-592F-4341-BE77-C7CCE7ABA01C}" name="recruitment" dataDxfId="65"/>
-    <tableColumn id="11" xr3:uid="{42EBEB42-55DC-4794-B920-10571329E548}" name="country" dataDxfId="64"/>
-    <tableColumn id="12" xr3:uid="{3DA789C7-1F7F-4F5A-9071-3AF173BB5D6D}" name="cities" dataDxfId="63"/>
-    <tableColumn id="13" xr3:uid="{B64E54F6-23E4-48D1-9AC6-D7F2085369F2}" name="whoregion" dataDxfId="62"/>
-    <tableColumn id="18" xr3:uid="{5AFCCA19-88CD-4E14-9F77-421B4C1A8F81}" name="representative" dataDxfId="61"/>
-    <tableColumn id="19" xr3:uid="{72D94544-8A93-4CF3-AB54-01C46F289B2E}" name="adjust" dataDxfId="60"/>
-    <tableColumn id="15" xr3:uid="{ECB5BCAC-0E8F-4309-9657-6E52DA7E4357}" name="design" dataDxfId="59"/>
-    <tableColumn id="14" xr3:uid="{84C85747-43B8-49AE-BF7E-E45FF2C0EB1C}" name="rob_score_3cat" dataDxfId="58"/>
-    <tableColumn id="22" xr3:uid="{A4C5FA94-6595-4DD3-BE58-DEFF4B424983}" name="sw_time_frame" dataDxfId="57"/>
-    <tableColumn id="23" xr3:uid="{4996C400-7810-4139-88C2-EA81239DAE76}" name="fsw_prop" dataDxfId="56"/>
-    <tableColumn id="24" xr3:uid="{F61C4FD5-BE99-46D0-949E-337D748D4C39}" name="hiv_num" dataDxfId="55"/>
-    <tableColumn id="25" xr3:uid="{A8221E34-1F43-4C50-B47B-16C9C7B932AA}" name="hiv_perc" dataDxfId="54"/>
-    <tableColumn id="26" xr3:uid="{EC7E25D4-FC36-40AB-BB1F-C3760A928509}" name="exposure_type" dataDxfId="53"/>
-    <tableColumn id="27" xr3:uid="{5C102B93-1F59-4E15-86CD-285B299CE839}" name="exposure_definition" dataDxfId="52"/>
-    <tableColumn id="28" xr3:uid="{91F32478-8EB3-4371-828B-3A60C0FF24FC}" name="exposure_definition_short" dataDxfId="51"/>
-    <tableColumn id="29" xr3:uid="{148DCEC7-8CD8-4622-9F76-AED527E14106}" name="exposure_time_frame" dataDxfId="50"/>
-    <tableColumn id="30" xr3:uid="{629B4CD8-CA00-4F8E-95FF-0FC82A720E8D}" name="exposure_tf_bin" dataDxfId="49"/>
-    <tableColumn id="31" xr3:uid="{EDFCDBDF-FEEB-4B91-8923-C2F89D21A567}" name="perpetrator" dataDxfId="48"/>
-    <tableColumn id="32" xr3:uid="{4C2A8059-83A9-41C4-A898-105614C56D7B}" name="exposed_num" dataDxfId="47"/>
-    <tableColumn id="33" xr3:uid="{9FBD19E7-3910-40C0-AE9F-6A87DE9DAD9A}" name="exposed_perc" dataDxfId="46"/>
-    <tableColumn id="85" xr3:uid="{E7952545-C72B-4BA5-8AAC-E47CAA11660B}" name="use_exposed" dataDxfId="45"/>
-    <tableColumn id="34" xr3:uid="{8DE318B8-C001-40B3-99AF-1EAC67EE124D}" name="outcome" dataDxfId="44"/>
-    <tableColumn id="35" xr3:uid="{1B673DA4-B0CE-456F-BE37-E6B68421B29D}" name="outcome_definition" dataDxfId="43"/>
-    <tableColumn id="81" xr3:uid="{0EB9D9DA-9F9D-4B59-9180-0C9D8C18FFA7}" name="outcome_bin" dataDxfId="42"/>
-    <tableColumn id="82" xr3:uid="{279E3393-30BA-42FE-B8EE-3C12AD82EA0C}" name="outcome_definition_short" dataDxfId="41"/>
-    <tableColumn id="83" xr3:uid="{51E32F51-F88E-4FD2-B7A7-5F3105FF0C05}" name="current" dataDxfId="40"/>
-    <tableColumn id="84" xr3:uid="{034BA84B-6F2A-432B-AFE3-04E26C6C5CBF}" name="outcome_denominator" dataDxfId="39"/>
-    <tableColumn id="36" xr3:uid="{D7ED8F26-F483-4FB4-A5F6-410210E8E035}" name="outcome_time_frame" dataDxfId="38"/>
-    <tableColumn id="37" xr3:uid="{98023959-BBB5-4F30-9B52-A26ED97CA46D}" name="outcome_tf_bin" dataDxfId="37"/>
-    <tableColumn id="38" xr3:uid="{290186E4-1313-47BC-85E4-E8A272937437}" name="adj" dataDxfId="36"/>
-    <tableColumn id="39" xr3:uid="{1B94AA8C-775F-4F43-8C0B-C4C5FC73BE83}" name="effect_best_model" dataDxfId="35"/>
-    <tableColumn id="40" xr3:uid="{9FDFB3A9-96FB-4CCC-96B3-14E8F1E7F084}" name="effect_best" dataDxfId="34"/>
-    <tableColumn id="41" xr3:uid="{24EBBDFA-5954-4CFE-AE11-4786819F4817}" name="effect_best_lower" dataDxfId="33"/>
-    <tableColumn id="42" xr3:uid="{04872BBE-FF1D-48E7-81DE-F2964BB9A901}" name="effect_best_upper" dataDxfId="32"/>
-    <tableColumn id="43" xr3:uid="{AA1D0F06-5876-400D-AEC4-A9BA51186BB4}" name="una_effect" dataDxfId="31"/>
-    <tableColumn id="44" xr3:uid="{2E1B35E6-790B-4FD1-B218-D62562954D2C}" name="unadj_est" dataDxfId="30"/>
-    <tableColumn id="45" xr3:uid="{863FF24D-DDA7-4AEC-8E56-D2B1CF50E956}" name="un_lower" dataDxfId="29"/>
-    <tableColumn id="46" xr3:uid="{7E6F6753-7AE6-4B33-8928-321EA4A75206}" name="un_upper" dataDxfId="28"/>
-    <tableColumn id="47" xr3:uid="{B3E1FADB-3545-4209-B53C-C3E6D14BD97C}" name="un_p_val" dataDxfId="27"/>
-    <tableColumn id="48" xr3:uid="{60DDE3D6-CF7B-4A99-B8D8-2414158716A4}" name="adj_effect" dataDxfId="26"/>
-    <tableColumn id="49" xr3:uid="{2123EDDE-3630-4413-80BC-93CF07EBA59D}" name="adj_est" dataDxfId="25"/>
-    <tableColumn id="50" xr3:uid="{E63F400A-FDF0-4DD5-ABB2-83E3C804C286}" name="adj_lower" dataDxfId="24"/>
-    <tableColumn id="51" xr3:uid="{B0C6D5F8-5715-419F-A29E-24F642663472}" name="adj_upper" dataDxfId="23"/>
-    <tableColumn id="52" xr3:uid="{09D02A5C-2B0E-4B5B-9E00-570650DBEE7A}" name="adj_p_val" dataDxfId="22"/>
-    <tableColumn id="53" xr3:uid="{890D9196-A129-43E6-81DD-D8AB87917755}" name="adjusted_for" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{63BDA606-9089-4874-B591-0807542982B0}" name="study" dataDxfId="76"/>
+    <tableColumn id="2" xr3:uid="{4AA8E6CE-2FAC-4107-B8DC-6C83DCBCB093}" name="title" dataDxfId="75"/>
+    <tableColumn id="3" xr3:uid="{14CAD349-3AE5-4AAE-B62E-AB16344DCD7A}" name="author" dataDxfId="74"/>
+    <tableColumn id="4" xr3:uid="{8E5BD801-3765-44D8-9626-6C5BDF351F18}" name="year" dataDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{81893C14-3975-4E03-80A3-DE30289BF32A}" name="pre_2016" dataDxfId="72"/>
+    <tableColumn id="86" xr3:uid="{3885C3B9-A9A0-4B9E-9BFD-8F101CACF3DE}" name="pre2017" dataDxfId="71"/>
+    <tableColumn id="17" xr3:uid="{322147C7-85C6-4C86-A8E1-DC3ADD324E36}" name="rayyan" dataDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{FFBFAFB5-D941-4514-8EA1-91C9AAF90EBD}" name="pub_type" dataDxfId="69"/>
+    <tableColumn id="7" xr3:uid="{69E1E0B1-F32D-4F7A-A87A-9A5482EA93C4}" name="study_design" dataDxfId="68"/>
+    <tableColumn id="8" xr3:uid="{75FFCE04-2838-42F3-B6A4-F84704B19B2A}" name="study_setting" dataDxfId="67"/>
+    <tableColumn id="16" xr3:uid="{56FD4B42-21B3-4295-B6F9-3507E9D803B6}" name="overall_sample_size" dataDxfId="66"/>
+    <tableColumn id="9" xr3:uid="{35FF46C8-B4AA-4BA5-BDA2-9A64E443ED8B}" name="analytical_sample_size" dataDxfId="65"/>
+    <tableColumn id="10" xr3:uid="{4B153F2C-592F-4341-BE77-C7CCE7ABA01C}" name="recruitment" dataDxfId="64"/>
+    <tableColumn id="11" xr3:uid="{42EBEB42-55DC-4794-B920-10571329E548}" name="country" dataDxfId="63"/>
+    <tableColumn id="12" xr3:uid="{3DA789C7-1F7F-4F5A-9071-3AF173BB5D6D}" name="cities" dataDxfId="62"/>
+    <tableColumn id="13" xr3:uid="{B64E54F6-23E4-48D1-9AC6-D7F2085369F2}" name="whoregion" dataDxfId="61"/>
+    <tableColumn id="18" xr3:uid="{5AFCCA19-88CD-4E14-9F77-421B4C1A8F81}" name="representative" dataDxfId="60"/>
+    <tableColumn id="19" xr3:uid="{72D94544-8A93-4CF3-AB54-01C46F289B2E}" name="adjust" dataDxfId="59"/>
+    <tableColumn id="15" xr3:uid="{ECB5BCAC-0E8F-4309-9657-6E52DA7E4357}" name="design" dataDxfId="58"/>
+    <tableColumn id="14" xr3:uid="{84C85747-43B8-49AE-BF7E-E45FF2C0EB1C}" name="rob_score_3cat" dataDxfId="57"/>
+    <tableColumn id="22" xr3:uid="{A4C5FA94-6595-4DD3-BE58-DEFF4B424983}" name="sw_time_frame" dataDxfId="56"/>
+    <tableColumn id="23" xr3:uid="{4996C400-7810-4139-88C2-EA81239DAE76}" name="fsw_prop" dataDxfId="55"/>
+    <tableColumn id="24" xr3:uid="{F61C4FD5-BE99-46D0-949E-337D748D4C39}" name="hiv_num" dataDxfId="54"/>
+    <tableColumn id="25" xr3:uid="{A8221E34-1F43-4C50-B47B-16C9C7B932AA}" name="hiv_perc" dataDxfId="53"/>
+    <tableColumn id="26" xr3:uid="{EC7E25D4-FC36-40AB-BB1F-C3760A928509}" name="exposure_type" dataDxfId="52"/>
+    <tableColumn id="27" xr3:uid="{5C102B93-1F59-4E15-86CD-285B299CE839}" name="exposure_definition" dataDxfId="51"/>
+    <tableColumn id="28" xr3:uid="{91F32478-8EB3-4371-828B-3A60C0FF24FC}" name="exposure_definition_short" dataDxfId="50"/>
+    <tableColumn id="29" xr3:uid="{148DCEC7-8CD8-4622-9F76-AED527E14106}" name="exposure_time_frame" dataDxfId="49"/>
+    <tableColumn id="30" xr3:uid="{629B4CD8-CA00-4F8E-95FF-0FC82A720E8D}" name="exposure_tf_bin" dataDxfId="48"/>
+    <tableColumn id="31" xr3:uid="{EDFCDBDF-FEEB-4B91-8923-C2F89D21A567}" name="perpetrator" dataDxfId="47"/>
+    <tableColumn id="32" xr3:uid="{4C2A8059-83A9-41C4-A898-105614C56D7B}" name="exposed_num" dataDxfId="46"/>
+    <tableColumn id="33" xr3:uid="{9FBD19E7-3910-40C0-AE9F-6A87DE9DAD9A}" name="exposed_perc" dataDxfId="45"/>
+    <tableColumn id="85" xr3:uid="{E7952545-C72B-4BA5-8AAC-E47CAA11660B}" name="use_exposed" dataDxfId="44"/>
+    <tableColumn id="34" xr3:uid="{8DE318B8-C001-40B3-99AF-1EAC67EE124D}" name="outcome" dataDxfId="43"/>
+    <tableColumn id="35" xr3:uid="{1B673DA4-B0CE-456F-BE37-E6B68421B29D}" name="outcome_definition" dataDxfId="42"/>
+    <tableColumn id="81" xr3:uid="{0EB9D9DA-9F9D-4B59-9180-0C9D8C18FFA7}" name="outcome_bin" dataDxfId="41"/>
+    <tableColumn id="82" xr3:uid="{279E3393-30BA-42FE-B8EE-3C12AD82EA0C}" name="outcome_definition_short" dataDxfId="40"/>
+    <tableColumn id="83" xr3:uid="{51E32F51-F88E-4FD2-B7A7-5F3105FF0C05}" name="current" dataDxfId="39"/>
+    <tableColumn id="84" xr3:uid="{034BA84B-6F2A-432B-AFE3-04E26C6C5CBF}" name="outcome_denominator" dataDxfId="38"/>
+    <tableColumn id="36" xr3:uid="{D7ED8F26-F483-4FB4-A5F6-410210E8E035}" name="outcome_time_frame" dataDxfId="37"/>
+    <tableColumn id="37" xr3:uid="{98023959-BBB5-4F30-9B52-A26ED97CA46D}" name="outcome_tf_bin" dataDxfId="36"/>
+    <tableColumn id="38" xr3:uid="{290186E4-1313-47BC-85E4-E8A272937437}" name="adj" dataDxfId="35"/>
+    <tableColumn id="39" xr3:uid="{1B94AA8C-775F-4F43-8C0B-C4C5FC73BE83}" name="effect_best_model" dataDxfId="34"/>
+    <tableColumn id="40" xr3:uid="{9FDFB3A9-96FB-4CCC-96B3-14E8F1E7F084}" name="effect_best" dataDxfId="33"/>
+    <tableColumn id="41" xr3:uid="{24EBBDFA-5954-4CFE-AE11-4786819F4817}" name="effect_best_lower" dataDxfId="32"/>
+    <tableColumn id="42" xr3:uid="{04872BBE-FF1D-48E7-81DE-F2964BB9A901}" name="effect_best_upper" dataDxfId="31"/>
+    <tableColumn id="43" xr3:uid="{AA1D0F06-5876-400D-AEC4-A9BA51186BB4}" name="una_effect" dataDxfId="30"/>
+    <tableColumn id="44" xr3:uid="{2E1B35E6-790B-4FD1-B218-D62562954D2C}" name="unadj_est" dataDxfId="29"/>
+    <tableColumn id="45" xr3:uid="{863FF24D-DDA7-4AEC-8E56-D2B1CF50E956}" name="un_lower" dataDxfId="28"/>
+    <tableColumn id="46" xr3:uid="{7E6F6753-7AE6-4B33-8928-321EA4A75206}" name="un_upper" dataDxfId="27"/>
+    <tableColumn id="47" xr3:uid="{B3E1FADB-3545-4209-B53C-C3E6D14BD97C}" name="un_p_val" dataDxfId="26"/>
+    <tableColumn id="48" xr3:uid="{60DDE3D6-CF7B-4A99-B8D8-2414158716A4}" name="adj_effect" dataDxfId="25"/>
+    <tableColumn id="49" xr3:uid="{2123EDDE-3630-4413-80BC-93CF07EBA59D}" name="adj_est" dataDxfId="24"/>
+    <tableColumn id="50" xr3:uid="{E63F400A-FDF0-4DD5-ABB2-83E3C804C286}" name="adj_lower" dataDxfId="23"/>
+    <tableColumn id="51" xr3:uid="{B0C6D5F8-5715-419F-A29E-24F642663472}" name="adj_upper" dataDxfId="22"/>
+    <tableColumn id="52" xr3:uid="{09D02A5C-2B0E-4B5B-9E00-570650DBEE7A}" name="adj_p_val" dataDxfId="21"/>
+    <tableColumn id="53" xr3:uid="{890D9196-A129-43E6-81DD-D8AB87917755}" name="adjusted_for" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5D1825D9-EB95-4810-9253-F86B5C0B7773}" name="Table13" displayName="Table13" ref="A1:R222" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5D1825D9-EB95-4810-9253-F86B5C0B7773}" name="Table13" displayName="Table13" ref="A1:R222" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="A1:R222" xr:uid="{70179EDD-82C2-49C7-80B9-689E0A41FA4C}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R222">
     <sortCondition ref="A1:A222"/>
   </sortState>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{681258BE-51F4-45D3-A868-AF1A9746554D}" name="study" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{20ED1BD1-C5C9-47EF-9064-32DB67312A11}" name="title" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{3F6A0D0B-4869-4372-A299-38B911293F95}" name="author" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{8B05C4BB-4396-46D0-883D-E81650ED4F19}" name="year" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{B6766C1B-0781-46D6-9050-7C522D126965}" name="design" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{AF1D15F6-C5AA-442B-9EB0-2C61875D0D41}" name="study_setting" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{C5115314-8A25-4916-8E4A-6443FDF9788B}" name="recruitment" dataDxfId="12"/>
-    <tableColumn id="26" xr3:uid="{BF7347A3-5CB7-467B-B8DA-8AE08A490D68}" name="exposure_type" dataDxfId="11"/>
-    <tableColumn id="27" xr3:uid="{87907FAD-028A-4D52-918D-9DAA322B243B}" name="exposure_definition" dataDxfId="10"/>
-    <tableColumn id="28" xr3:uid="{470F19C0-0790-41C9-BE26-EF6FB1CAD754}" name="exposure_definition_short" dataDxfId="9"/>
-    <tableColumn id="29" xr3:uid="{17C7BBA6-9E54-4860-B93E-3ECD48916913}" name="exposure_time_frame" dataDxfId="8"/>
-    <tableColumn id="30" xr3:uid="{1CC5D145-D5CB-4691-8902-647DD7E7DAB6}" name="exposure_tf_bin" dataDxfId="7"/>
-    <tableColumn id="31" xr3:uid="{BF997D6E-0A29-4A5B-B40F-2326274C06EF}" name="perpetrator" dataDxfId="6"/>
-    <tableColumn id="38" xr3:uid="{AA580DAB-9DA8-4134-912A-92B803D2A57E}" name="adj" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{71DC3936-A548-4D1F-B1FF-F3C6CD28BDEA}" name="representative" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{6F9F8390-DD06-47E3-AD07-5B3F4BB20067}" name="design2" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{681258BE-51F4-45D3-A868-AF1A9746554D}" name="study" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{20ED1BD1-C5C9-47EF-9064-32DB67312A11}" name="title" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{3F6A0D0B-4869-4372-A299-38B911293F95}" name="author" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{8B05C4BB-4396-46D0-883D-E81650ED4F19}" name="year" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{B6766C1B-0781-46D6-9050-7C522D126965}" name="design" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{AF1D15F6-C5AA-442B-9EB0-2C61875D0D41}" name="study_setting" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{C5115314-8A25-4916-8E4A-6443FDF9788B}" name="recruitment" dataDxfId="11"/>
+    <tableColumn id="26" xr3:uid="{BF7347A3-5CB7-467B-B8DA-8AE08A490D68}" name="exposure_type" dataDxfId="10"/>
+    <tableColumn id="27" xr3:uid="{87907FAD-028A-4D52-918D-9DAA322B243B}" name="exposure_definition" dataDxfId="9"/>
+    <tableColumn id="28" xr3:uid="{470F19C0-0790-41C9-BE26-EF6FB1CAD754}" name="exposure_definition_short" dataDxfId="8"/>
+    <tableColumn id="29" xr3:uid="{17C7BBA6-9E54-4860-B93E-3ECD48916913}" name="exposure_time_frame" dataDxfId="7"/>
+    <tableColumn id="30" xr3:uid="{1CC5D145-D5CB-4691-8902-647DD7E7DAB6}" name="exposure_tf_bin" dataDxfId="6"/>
+    <tableColumn id="31" xr3:uid="{BF997D6E-0A29-4A5B-B40F-2326274C06EF}" name="perpetrator" dataDxfId="5"/>
+    <tableColumn id="38" xr3:uid="{AA580DAB-9DA8-4134-912A-92B803D2A57E}" name="adj" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{71DC3936-A548-4D1F-B1FF-F3C6CD28BDEA}" name="representative" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{6F9F8390-DD06-47E3-AD07-5B3F4BB20067}" name="design2" dataDxfId="2">
       <calculatedColumnFormula>IF(Table13[[#This Row],[design]]="Cross-sectional",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{ABA2DD5F-84E9-47B4-84B0-280178B26041}" name="adjust" dataDxfId="2">
+    <tableColumn id="5" xr3:uid="{ABA2DD5F-84E9-47B4-84B0-280178B26041}" name="adjust" dataDxfId="1">
       <calculatedColumnFormula>IF(Table13[[#This Row],[adj]]="Adjusted",1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{09DD9ACD-5E28-473D-8453-26BEC5313869}" name="rob_score_3cat" dataDxfId="1"/>
+    <tableColumn id="15" xr3:uid="{09DD9ACD-5E28-473D-8453-26BEC5313869}" name="rob_score_3cat" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9783,160 +9783,16 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="AB2" dT="2025-11-25T14:21:24.30" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{6077D12D-0822-4C1B-A082-34FDBDF12D7D}" done="1">
-    <text>It should be possible to use the results in tables 2 and 3 to create a variable for “Any violent experiences” which would be more useful than this</text>
-  </threadedComment>
-  <threadedComment ref="AB2" dT="2025-12-09T20:38:38.71" personId="{BAA1B8CF-6869-42EE-8BDA-0BD94C78970E}" id="{9641B70B-A34D-4810-874B-415BFFC642D9}" parentId="{6077D12D-0822-4C1B-A082-34FDBDF12D7D}">
-    <text>Table 3 is condom use</text>
-  </threadedComment>
-  <threadedComment ref="AB2" dT="2025-12-09T20:39:18.59" personId="{BAA1B8CF-6869-42EE-8BDA-0BD94C78970E}" id="{795D1CEB-4B7D-481C-9AC3-306D54DDAF9A}" parentId="{6077D12D-0822-4C1B-A082-34FDBDF12D7D}">
-    <text>Table 4 is HIV but when I include it, I get an OR of 31.51. it’s a confusing study. Let’s discuss</text>
-  </threadedComment>
-  <threadedComment ref="AB2" dT="2025-12-10T11:46:14.39" personId="{BAA1B8CF-6869-42EE-8BDA-0BD94C78970E}" id="{F95F61BD-0C0C-4B32-B207-C516ABA93069}" parentId="{6077D12D-0822-4C1B-A082-34FDBDF12D7D}">
-    <text>Spoke to Jack and decided to keep as is because of adjusted ORs</text>
-  </threadedComment>
-  <threadedComment ref="AT12" dT="2025-11-21T10:53:32.45" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{914EC8C3-060D-4CAD-AEEA-7C21592D51A2}" done="1">
-    <text>1.743</text>
-  </threadedComment>
-  <threadedComment ref="AU12" dT="2025-11-21T10:53:39.51" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{984A2285-FB9F-47C8-9AB5-E3FDB43CBA40}" done="1">
-    <text>1.002</text>
-  </threadedComment>
-  <threadedComment ref="AX12" dT="2025-11-21T10:53:32.45" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{36397AA6-56E0-46F1-9B8F-7D52A57FE877}" done="1">
-    <text>1.743</text>
-  </threadedComment>
-  <threadedComment ref="K18" dT="2025-11-26T16:55:05.62" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{FC96265B-1784-4414-A44D-8FF495448F25}" done="1">
-    <text>“Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</text>
-  </threadedComment>
-  <threadedComment ref="L18" dT="2025-11-26T16:55:05.62" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{3FC56194-C8C0-4C5B-9B4F-885AFC6B3104}" done="1">
-    <text>“Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</text>
-  </threadedComment>
-  <threadedComment ref="Y18" dT="2025-11-26T16:52:56.92" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{B4B5594F-3597-4CB9-98BA-2DF7AE10357D}" done="1">
-    <text>Back calculate from prevalence?</text>
-  </threadedComment>
-  <threadedComment ref="Z18" dT="2025-11-26T16:52:36.92" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{11FCD21A-07F0-4BD4-B5A8-66F97F50990E}" done="1">
-    <text>0.053? “HIV prevalence was estimated as 5.3% with a 95% confidence interval (CI) (4.4%–6.2%).“</text>
-  </threadedComment>
-  <threadedComment ref="K19" dT="2025-11-26T16:55:05.62" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{238EDB2C-16AF-4812-AD1B-6A07F1561048}" done="1">
-    <text>“Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</text>
-  </threadedComment>
-  <threadedComment ref="L19" dT="2025-11-26T16:55:05.62" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{E9D7F8BB-47CB-4D0B-B77C-B1AB387ABAC0}" done="1">
-    <text>“Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</text>
-  </threadedComment>
-  <threadedComment ref="Y19" dT="2025-11-26T16:52:56.92" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{397E0321-6508-471E-8C40-2D5D16A0D0DD}" done="1">
-    <text>Back calculate from prevalence?</text>
-  </threadedComment>
-  <threadedComment ref="Z19" dT="2025-11-26T16:52:36.92" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{586E2BF3-6B79-4E45-9DD6-696F2DA503A8}" done="1">
-    <text>0.053? “HIV prevalence was estimated as 5.3% with a 95% confidence interval (CI) (4.4%–6.2%).“</text>
-  </threadedComment>
-  <threadedComment ref="Z20" dT="2025-11-26T17:01:54.61" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{4C5CBF93-98BA-4F0A-A373-2ABD7A4802AE}" done="1">
-    <text>I could only see “The adjusted prevalence of HIV was 3.2% (95% CI 1.76–5.75).“</text>
-  </threadedComment>
-  <threadedComment ref="Z20" dT="2025-12-10T09:23:05.08" personId="{BAA1B8CF-6869-42EE-8BDA-0BD94C78970E}" id="{849E4246-81B6-47FC-8931-0534E9FCF31A}" parentId="{4C5CBF93-98BA-4F0A-A373-2ABD7A4802AE}">
-    <text>Table 1 shows 72 hiv+. Ask Jack whether we use adjusted or unadjusted</text>
-  </threadedComment>
-  <threadedComment ref="Z21" dT="2025-11-26T17:01:54.61" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{EAC91F3F-7C39-46E7-A671-022EE9C432E8}" done="1">
-    <text>I could only see “The adjusted prevalence of HIV was 3.2% (95% CI 1.76–5.75).“</text>
-  </threadedComment>
-  <threadedComment ref="A22" dT="2025-11-21T09:32:26.00" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{83CC3671-6338-4CD1-ABD8-4C9EC9003E41}" done="1">
-    <text>2019</text>
-  </threadedComment>
-  <threadedComment ref="D22" dT="2025-11-21T09:32:35.66" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{0E867546-6B89-4EFC-B072-7637D2BE57A1}" done="1">
-    <text>2019</text>
-  </threadedComment>
-  <threadedComment ref="A23" dT="2025-11-21T09:32:26.00" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{F62C4C7A-B342-40B1-A7EC-4AF2916C68F8}" done="1">
-    <text>2019</text>
-  </threadedComment>
-  <threadedComment ref="D23" dT="2025-11-21T09:32:35.66" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{C11FE7A7-D031-49C0-ADEC-B47D7669289D}" done="1">
-    <text>2019</text>
-  </threadedComment>
-  <threadedComment ref="AG24" dT="2025-11-21T11:56:31.15" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{B340D370-DD42-45C2-99F1-F392C636C507}" done="1">
-    <text>These are the number with outcome?</text>
-  </threadedComment>
-  <threadedComment ref="AG24" dT="2025-11-21T11:57:46.96" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{8A7F0066-F2B5-4B3F-8E10-21F29B1DE42B}" parentId="{B340D370-DD42-45C2-99F1-F392C636C507}">
-    <text>Not right</text>
-  </threadedComment>
-  <threadedComment ref="AH24" dT="2025-11-21T11:57:26.73" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{8F037DF1-D3F6-4675-B321-9444B3086129}" done="1">
-    <text>If this is what you are using when pooling then 60.4%</text>
-  </threadedComment>
-  <threadedComment ref="AO24" dT="2025-11-21T11:54:45.48" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{16B3F7F6-45FC-4058-87A4-8C65D2C81A62}" done="1">
-    <text>Self-report being HIV+</text>
-  </threadedComment>
-  <threadedComment ref="AO24" dT="2025-11-21T11:55:00.89" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{B889188F-B6A5-465E-915A-48E98704BC71}" parentId="{16B3F7F6-45FC-4058-87A4-8C65D2C81A62}">
-    <text>Does that meet inclusion criteria??</text>
-  </threadedComment>
-  <threadedComment ref="AX24" dT="2025-11-21T12:29:21.10" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{39113FCF-CD56-4E26-92B6-BE77DCA66775}" done="1">
-    <text>I think you cn work this out: 0.59 (0.20-1.72)</text>
-  </threadedComment>
-  <threadedComment ref="AG25" dT="2025-11-21T11:56:31.15" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{A9D7F15F-BE27-46D2-AD8B-80D032ABAF56}" done="1">
-    <text>These are the number with outcome?</text>
-  </threadedComment>
-  <threadedComment ref="AG25" dT="2025-11-21T11:57:46.96" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{801CB555-1650-49FD-A5E8-C2A4E23E17AB}" parentId="{A9D7F15F-BE27-46D2-AD8B-80D032ABAF56}">
-    <text>Not right</text>
-  </threadedComment>
-  <threadedComment ref="AH25" dT="2025-11-21T11:57:26.73" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{259EC1F6-3229-4043-BBD1-D170A8630285}" done="1">
-    <text>If this is what you are using when pooling then 60.4%</text>
-  </threadedComment>
-  <threadedComment ref="AO25" dT="2025-11-21T11:55:13.11" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{DFFEADBE-C45A-440E-ACB5-5C739F26F7FD}" done="1">
-    <text>Self report HIV negative</text>
-  </threadedComment>
-  <threadedComment ref="AX25" dT="2025-11-21T12:12:36.07" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{77278C7A-E665-495E-9F77-ECFB90597AB7}" done="1">
-    <text>I think you can work this out: 0.83 (0.66-1.05)</text>
-  </threadedComment>
-  <threadedComment ref="AX25" dT="2025-12-01T16:49:48.78" personId="{BAA1B8CF-6869-42EE-8BDA-0BD94C78970E}" id="{810112EB-C58A-4D75-8005-4CB86F28D63B}" parentId="{77278C7A-E665-495E-9F77-ECFB90597AB7}">
-    <text>Well done</text>
-  </threadedComment>
-  <threadedComment ref="L30" dT="2025-11-27T14:14:36.38" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{CC904001-032B-4B72-B329-5D6E2173ADEE}" done="1">
-    <text>937</text>
-  </threadedComment>
-  <threadedComment ref="L31" dT="2025-11-27T14:14:55.99" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{A74F3F70-F7D7-48F9-A871-46F055A588F2}" done="1">
-    <text>740</text>
-  </threadedComment>
-  <threadedComment ref="L32" dT="2025-11-27T14:12:17.60" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{789FF504-3E8E-486F-97E3-8B97C7BDF7CD}" done="1">
-    <text>937</text>
-  </threadedComment>
-  <threadedComment ref="L34" dT="2025-11-27T14:14:15.43" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{F9CD37FE-3B73-48E9-8D33-F153AB42EC13}" done="1">
-    <text>735</text>
-  </threadedComment>
-  <threadedComment ref="L35" dT="2025-11-27T14:15:09.29" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{FAD2C12C-D163-4465-B27A-15F1F4A037DF}" done="1">
-    <text>735</text>
-  </threadedComment>
-  <threadedComment ref="L36" dT="2025-11-27T14:14:01.37" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{82578D19-7394-4157-8AD4-0B3777DC7B48}" done="1">
-    <text>937</text>
-  </threadedComment>
-  <threadedComment ref="L37" dT="2025-11-27T14:15:19.29" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{02D548A8-CEC1-42B7-8CC9-BFF35A1AEEF0}" done="1">
-    <text>739</text>
-  </threadedComment>
-  <threadedComment ref="L38" dT="2025-11-25T11:25:38.11" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{AE0B9FF2-A8F9-44EE-96BF-A77B61D12DA8}" done="1">
-    <text>453 “Living with HIV” table 4</text>
-  </threadedComment>
-  <threadedComment ref="BC38" dT="2025-11-25T09:53:58.37" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{34CB3925-8D93-473E-AE72-BB45AB11435B}" done="1">
-    <text>Not useable, HIV was not outcome in adjusted model.</text>
-  </threadedComment>
-  <threadedComment ref="BC38" dT="2025-12-09T16:25:16.35" personId="{BAA1B8CF-6869-42EE-8BDA-0BD94C78970E}" id="{E5B47665-DEC0-4DCD-8BD0-9BF20B0F7A77}" parentId="{34CB3925-8D93-473E-AE72-BB45AB11435B}">
-    <text>ok</text>
-  </threadedComment>
-  <threadedComment ref="L39" dT="2025-11-25T11:24:10.31" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{6B0D38DB-8812-4147-8FA9-F01465132932}" done="1">
-    <text>453 “Living with HIV” table 4</text>
-  </threadedComment>
-  <threadedComment ref="L40" dT="2025-11-25T11:24:53.13" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{C9B78CB0-D806-48C0-AD9B-84EF2C8A0988}" done="1">
-    <text>462 “Ever tested for HIV” table 4</text>
-  </threadedComment>
-  <threadedComment ref="L41" dT="2025-11-25T11:23:52.21" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{D67639CC-A123-41EA-9BF6-0A796AAF68CD}" done="1">
-    <text>462 “Ever tested for HIV” table 4</text>
-  </threadedComment>
-  <threadedComment ref="BG42" dT="2025-11-25T08:43:16.35" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{1528D086-EBFF-425B-8127-14D43A4FCA75}" done="1">
-    <text>Alcohol use, STIs, type of sexual intercourse</text>
-  </threadedComment>
-  <threadedComment ref="A44" dT="2025-11-21T10:07:49.22" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{E7048C25-104E-4675-A95C-E812B6DD6BF4}" done="1">
+  <threadedComment ref="A2" dT="2025-11-21T10:07:49.22" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{E7048C25-104E-4675-A95C-E812B6DD6BF4}" done="1">
     <text>ALL TGW - is that allowed in the review??</text>
   </threadedComment>
-  <threadedComment ref="A44" dT="2025-11-21T10:13:22.30" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{A0D563AF-D07D-4951-A6FA-49CAAB630554}" parentId="{E7048C25-104E-4675-A95C-E812B6DD6BF4}">
+  <threadedComment ref="A2" dT="2025-11-21T10:13:22.30" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{A0D563AF-D07D-4951-A6FA-49CAAB630554}" parentId="{E7048C25-104E-4675-A95C-E812B6DD6BF4}">
     <text>Strange this study isnt in the MSM/TGW review</text>
   </threadedComment>
-  <threadedComment ref="X44" dT="2025-11-21T10:05:40.09" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{2F62E598-90C6-4D82-AB67-B976649E5C79}" done="1">
+  <threadedComment ref="X2" dT="2025-11-21T10:05:40.09" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{2F62E598-90C6-4D82-AB67-B976649E5C79}" done="1">
     <text>0.7424</text>
   </threadedComment>
-  <threadedComment ref="AB44" dT="2025-11-21T10:06:47.48" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{783D4DD9-BAF3-4346-92DB-B69617C5AFF1}" done="1">
+  <threadedComment ref="AB2" dT="2025-11-21T10:06:47.48" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{783D4DD9-BAF3-4346-92DB-B69617C5AFF1}" done="1">
     <text>Ex-
 posure to violence was measured through two questions: re-
 spondents were asked if in the last 12 months they had been
@@ -9944,10 +9800,10 @@
 Respondents answering yes to either question were coded as
 1 and the remaining respondents were coded as 0.</text>
   </threadedComment>
-  <threadedComment ref="AB44" dT="2025-11-21T10:07:29.46" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{493A1970-9296-454D-A941-8335A9C55183}" parentId="{783D4DD9-BAF3-4346-92DB-B69617C5AFF1}">
+  <threadedComment ref="AB2" dT="2025-11-21T10:07:29.46" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{493A1970-9296-454D-A941-8335A9C55183}" parentId="{783D4DD9-BAF3-4346-92DB-B69617C5AFF1}">
     <text>Beaten or raped in past year</text>
   </threadedComment>
-  <threadedComment ref="AC44" dT="2025-11-21T10:06:52.50" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{08F9D07E-6013-4A64-82E7-E46D2826F100}" done="1">
+  <threadedComment ref="AC2" dT="2025-11-21T10:06:52.50" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{08F9D07E-6013-4A64-82E7-E46D2826F100}" done="1">
     <text>Ex-
 posure to violence was measured through two questions: re-
 spondents were asked if in the last 12 months they had been
@@ -9955,15 +9811,159 @@
 Respondents answering yes to either question were coded as
 1 and the remaining respondents were coded as 0.</text>
   </threadedComment>
-  <threadedComment ref="AC44" dT="2025-11-21T10:07:09.22" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{8B116C4B-B802-44CE-96BA-91E0CC385C92}" parentId="{08F9D07E-6013-4A64-82E7-E46D2826F100}">
+  <threadedComment ref="AC2" dT="2025-11-21T10:07:09.22" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{8B116C4B-B802-44CE-96BA-91E0CC385C92}" parentId="{08F9D07E-6013-4A64-82E7-E46D2826F100}">
     <text>Beaten/raped in past year</text>
   </threadedComment>
-  <threadedComment ref="AU44" dT="2025-11-21T10:12:43.60" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{268C0D53-D6A6-4E59-9995-8C6ED708B105}" done="1">
+  <threadedComment ref="AU2" dT="2025-11-21T10:12:43.60" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{268C0D53-D6A6-4E59-9995-8C6ED708B105}" done="1">
     <text xml:space="preserve">1.185
 </text>
   </threadedComment>
-  <threadedComment ref="AV44" dT="2025-11-21T10:12:56.06" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{60996FA8-6F37-421F-B95D-D8A8C1756904}" done="1">
+  <threadedComment ref="AV2" dT="2025-11-21T10:12:56.06" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{60996FA8-6F37-421F-B95D-D8A8C1756904}" done="1">
     <text>8.388</text>
+  </threadedComment>
+  <threadedComment ref="AB3" dT="2025-11-25T14:21:24.30" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{6077D12D-0822-4C1B-A082-34FDBDF12D7D}" done="1">
+    <text>It should be possible to use the results in tables 2 and 3 to create a variable for “Any violent experiences” which would be more useful than this</text>
+  </threadedComment>
+  <threadedComment ref="AB3" dT="2025-12-09T20:38:38.71" personId="{BAA1B8CF-6869-42EE-8BDA-0BD94C78970E}" id="{9641B70B-A34D-4810-874B-415BFFC642D9}" parentId="{6077D12D-0822-4C1B-A082-34FDBDF12D7D}">
+    <text>Table 3 is condom use</text>
+  </threadedComment>
+  <threadedComment ref="AB3" dT="2025-12-09T20:39:18.59" personId="{BAA1B8CF-6869-42EE-8BDA-0BD94C78970E}" id="{795D1CEB-4B7D-481C-9AC3-306D54DDAF9A}" parentId="{6077D12D-0822-4C1B-A082-34FDBDF12D7D}">
+    <text>Table 4 is HIV but when I include it, I get an OR of 31.51. it’s a confusing study. Let’s discuss</text>
+  </threadedComment>
+  <threadedComment ref="AB3" dT="2025-12-10T11:46:14.39" personId="{BAA1B8CF-6869-42EE-8BDA-0BD94C78970E}" id="{F95F61BD-0C0C-4B32-B207-C516ABA93069}" parentId="{6077D12D-0822-4C1B-A082-34FDBDF12D7D}">
+    <text>Spoke to Jack and decided to keep as is because of adjusted ORs</text>
+  </threadedComment>
+  <threadedComment ref="AT13" dT="2025-11-21T10:53:32.45" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{914EC8C3-060D-4CAD-AEEA-7C21592D51A2}" done="1">
+    <text>1.743</text>
+  </threadedComment>
+  <threadedComment ref="AU13" dT="2025-11-21T10:53:39.51" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{984A2285-FB9F-47C8-9AB5-E3FDB43CBA40}" done="1">
+    <text>1.002</text>
+  </threadedComment>
+  <threadedComment ref="AX13" dT="2025-11-21T10:53:32.45" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{36397AA6-56E0-46F1-9B8F-7D52A57FE877}" done="1">
+    <text>1.743</text>
+  </threadedComment>
+  <threadedComment ref="K19" dT="2025-11-26T16:55:05.62" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{FC96265B-1784-4414-A44D-8FF495448F25}" done="1">
+    <text>“Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</text>
+  </threadedComment>
+  <threadedComment ref="L19" dT="2025-11-26T16:55:05.62" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{3FC56194-C8C0-4C5B-9B4F-885AFC6B3104}" done="1">
+    <text>“Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</text>
+  </threadedComment>
+  <threadedComment ref="Y19" dT="2025-11-26T16:52:56.92" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{B4B5594F-3597-4CB9-98BA-2DF7AE10357D}" done="1">
+    <text>Back calculate from prevalence?</text>
+  </threadedComment>
+  <threadedComment ref="Z19" dT="2025-11-26T16:52:36.92" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{11FCD21A-07F0-4BD4-B5A8-66F97F50990E}" done="1">
+    <text>0.053? “HIV prevalence was estimated as 5.3% with a 95% confidence interval (CI) (4.4%–6.2%).“</text>
+  </threadedComment>
+  <threadedComment ref="K20" dT="2025-11-26T16:55:05.62" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{238EDB2C-16AF-4812-AD1B-6A07F1561048}" done="1">
+    <text>“Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</text>
+  </threadedComment>
+  <threadedComment ref="L20" dT="2025-11-26T16:55:05.62" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{E9D7F8BB-47CB-4D0B-B77C-B1AB387ABAC0}" done="1">
+    <text>“Data were collected on 4245 FSW recruited by respondent driven sampling (RDS).”</text>
+  </threadedComment>
+  <threadedComment ref="Y20" dT="2025-11-26T16:52:56.92" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{397E0321-6508-471E-8C40-2D5D16A0D0DD}" done="1">
+    <text>Back calculate from prevalence?</text>
+  </threadedComment>
+  <threadedComment ref="Z20" dT="2025-11-26T16:52:36.92" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{586E2BF3-6B79-4E45-9DD6-696F2DA503A8}" done="1">
+    <text>0.053? “HIV prevalence was estimated as 5.3% with a 95% confidence interval (CI) (4.4%–6.2%).“</text>
+  </threadedComment>
+  <threadedComment ref="Z21" dT="2025-11-26T17:01:54.61" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{4C5CBF93-98BA-4F0A-A373-2ABD7A4802AE}" done="1">
+    <text>I could only see “The adjusted prevalence of HIV was 3.2% (95% CI 1.76–5.75).“</text>
+  </threadedComment>
+  <threadedComment ref="Z21" dT="2025-12-10T09:23:05.08" personId="{BAA1B8CF-6869-42EE-8BDA-0BD94C78970E}" id="{849E4246-81B6-47FC-8931-0534E9FCF31A}" parentId="{4C5CBF93-98BA-4F0A-A373-2ABD7A4802AE}">
+    <text>Table 1 shows 72 hiv+. Ask Jack whether we use adjusted or unadjusted</text>
+  </threadedComment>
+  <threadedComment ref="Z22" dT="2025-11-26T17:01:54.61" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{EAC91F3F-7C39-46E7-A671-022EE9C432E8}" done="1">
+    <text>I could only see “The adjusted prevalence of HIV was 3.2% (95% CI 1.76–5.75).“</text>
+  </threadedComment>
+  <threadedComment ref="A23" dT="2025-11-21T09:32:26.00" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{83CC3671-6338-4CD1-ABD8-4C9EC9003E41}" done="1">
+    <text>2019</text>
+  </threadedComment>
+  <threadedComment ref="D23" dT="2025-11-21T09:32:35.66" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{0E867546-6B89-4EFC-B072-7637D2BE57A1}" done="1">
+    <text>2019</text>
+  </threadedComment>
+  <threadedComment ref="A24" dT="2025-11-21T09:32:26.00" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{F62C4C7A-B342-40B1-A7EC-4AF2916C68F8}" done="1">
+    <text>2019</text>
+  </threadedComment>
+  <threadedComment ref="D24" dT="2025-11-21T09:32:35.66" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{C11FE7A7-D031-49C0-ADEC-B47D7669289D}" done="1">
+    <text>2019</text>
+  </threadedComment>
+  <threadedComment ref="AG25" dT="2025-11-21T11:56:31.15" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{B340D370-DD42-45C2-99F1-F392C636C507}" done="1">
+    <text>These are the number with outcome?</text>
+  </threadedComment>
+  <threadedComment ref="AG25" dT="2025-11-21T11:57:46.96" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{8A7F0066-F2B5-4B3F-8E10-21F29B1DE42B}" parentId="{B340D370-DD42-45C2-99F1-F392C636C507}">
+    <text>Not right</text>
+  </threadedComment>
+  <threadedComment ref="AH25" dT="2025-11-21T11:57:26.73" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{8F037DF1-D3F6-4675-B321-9444B3086129}" done="1">
+    <text>If this is what you are using when pooling then 60.4%</text>
+  </threadedComment>
+  <threadedComment ref="AO25" dT="2025-11-21T11:54:45.48" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{16B3F7F6-45FC-4058-87A4-8C65D2C81A62}" done="1">
+    <text>Self-report being HIV+</text>
+  </threadedComment>
+  <threadedComment ref="AO25" dT="2025-11-21T11:55:00.89" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{B889188F-B6A5-465E-915A-48E98704BC71}" parentId="{16B3F7F6-45FC-4058-87A4-8C65D2C81A62}">
+    <text>Does that meet inclusion criteria??</text>
+  </threadedComment>
+  <threadedComment ref="AX25" dT="2025-11-21T12:29:21.10" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{39113FCF-CD56-4E26-92B6-BE77DCA66775}" done="1">
+    <text>I think you cn work this out: 0.59 (0.20-1.72)</text>
+  </threadedComment>
+  <threadedComment ref="AG26" dT="2025-11-21T11:56:31.15" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{A9D7F15F-BE27-46D2-AD8B-80D032ABAF56}" done="1">
+    <text>These are the number with outcome?</text>
+  </threadedComment>
+  <threadedComment ref="AG26" dT="2025-11-21T11:57:46.96" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{801CB555-1650-49FD-A5E8-C2A4E23E17AB}" parentId="{A9D7F15F-BE27-46D2-AD8B-80D032ABAF56}">
+    <text>Not right</text>
+  </threadedComment>
+  <threadedComment ref="AH26" dT="2025-11-21T11:57:26.73" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{259EC1F6-3229-4043-BBD1-D170A8630285}" done="1">
+    <text>If this is what you are using when pooling then 60.4%</text>
+  </threadedComment>
+  <threadedComment ref="AO26" dT="2025-11-21T11:55:13.11" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{DFFEADBE-C45A-440E-ACB5-5C739F26F7FD}" done="1">
+    <text>Self report HIV negative</text>
+  </threadedComment>
+  <threadedComment ref="AX26" dT="2025-11-21T12:12:36.07" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{77278C7A-E665-495E-9F77-ECFB90597AB7}" done="1">
+    <text>I think you can work this out: 0.83 (0.66-1.05)</text>
+  </threadedComment>
+  <threadedComment ref="AX26" dT="2025-12-01T16:49:48.78" personId="{BAA1B8CF-6869-42EE-8BDA-0BD94C78970E}" id="{810112EB-C58A-4D75-8005-4CB86F28D63B}" parentId="{77278C7A-E665-495E-9F77-ECFB90597AB7}">
+    <text>Well done</text>
+  </threadedComment>
+  <threadedComment ref="L31" dT="2025-11-27T14:14:36.38" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{CC904001-032B-4B72-B329-5D6E2173ADEE}" done="1">
+    <text>937</text>
+  </threadedComment>
+  <threadedComment ref="L32" dT="2025-11-27T14:14:55.99" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{A74F3F70-F7D7-48F9-A871-46F055A588F2}" done="1">
+    <text>740</text>
+  </threadedComment>
+  <threadedComment ref="L33" dT="2025-11-27T14:12:17.60" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{789FF504-3E8E-486F-97E3-8B97C7BDF7CD}" done="1">
+    <text>937</text>
+  </threadedComment>
+  <threadedComment ref="L35" dT="2025-11-27T14:14:15.43" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{F9CD37FE-3B73-48E9-8D33-F153AB42EC13}" done="1">
+    <text>735</text>
+  </threadedComment>
+  <threadedComment ref="L36" dT="2025-11-27T14:15:09.29" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{FAD2C12C-D163-4465-B27A-15F1F4A037DF}" done="1">
+    <text>735</text>
+  </threadedComment>
+  <threadedComment ref="L37" dT="2025-11-27T14:14:01.37" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{82578D19-7394-4157-8AD4-0B3777DC7B48}" done="1">
+    <text>937</text>
+  </threadedComment>
+  <threadedComment ref="L38" dT="2025-11-27T14:15:19.29" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{02D548A8-CEC1-42B7-8CC9-BFF35A1AEEF0}" done="1">
+    <text>739</text>
+  </threadedComment>
+  <threadedComment ref="L39" dT="2025-11-25T11:25:38.11" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{AE0B9FF2-A8F9-44EE-96BF-A77B61D12DA8}" done="1">
+    <text>453 “Living with HIV” table 4</text>
+  </threadedComment>
+  <threadedComment ref="BC39" dT="2025-11-25T09:53:58.37" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{34CB3925-8D93-473E-AE72-BB45AB11435B}" done="1">
+    <text>Not useable, HIV was not outcome in adjusted model.</text>
+  </threadedComment>
+  <threadedComment ref="BC39" dT="2025-12-09T16:25:16.35" personId="{BAA1B8CF-6869-42EE-8BDA-0BD94C78970E}" id="{E5B47665-DEC0-4DCD-8BD0-9BF20B0F7A77}" parentId="{34CB3925-8D93-473E-AE72-BB45AB11435B}">
+    <text>ok</text>
+  </threadedComment>
+  <threadedComment ref="L40" dT="2025-11-25T11:24:10.31" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{6B0D38DB-8812-4147-8FA9-F01465132932}" done="1">
+    <text>453 “Living with HIV” table 4</text>
+  </threadedComment>
+  <threadedComment ref="L41" dT="2025-11-25T11:24:53.13" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{C9B78CB0-D806-48C0-AD9B-84EF2C8A0988}" done="1">
+    <text>462 “Ever tested for HIV” table 4</text>
+  </threadedComment>
+  <threadedComment ref="L42" dT="2025-11-25T11:23:52.21" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{D67639CC-A123-41EA-9BF6-0A796AAF68CD}" done="1">
+    <text>462 “Ever tested for HIV” table 4</text>
+  </threadedComment>
+  <threadedComment ref="BG43" dT="2025-11-25T08:43:16.35" personId="{DA9619AC-8416-4265-8990-FD11931F31BB}" id="{1528D086-EBFF-425B-8127-14D43A4FCA75}" done="1">
+    <text>Alcohol use, STIs, type of sexual intercourse</text>
   </threadedComment>
   <threadedComment ref="A45" dT="2025-11-21T15:35:36.47" personId="{9593CD56-7F84-4728-9BC0-6D79A344ADEB}" id="{B209DF1E-B64C-4C81-A700-7874271C29CF}" done="1">
     <text>Check if results for SW who are TGW are extracted?</text>
@@ -22557,22 +22557,22 @@
     </row>
     <row r="2" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>900</v>
+        <v>204</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>901</v>
+        <v>203</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>902</v>
+        <v>202</v>
       </c>
       <c r="D2" s="1">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="E2" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>1375</v>
@@ -22586,22 +22586,22 @@
       <c r="J2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>903</v>
-      </c>
-      <c r="L2" s="1">
-        <v>870</v>
+      <c r="K2" s="1">
+        <v>307</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>148</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>326</v>
+        <v>200</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" t="s">
         <v>1574</v>
       </c>
       <c r="Q2" s="1" t="s">
@@ -22620,52 +22620,52 @@
         <v>1</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="X2" s="1">
+        <v>0.74</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="AA2" s="1" t="s">
         <v>39</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>904</v>
+        <v>1433</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>905</v>
+        <v>1433</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="AF2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>906</v>
-      </c>
-      <c r="AH2" s="1">
-        <v>0.109</v>
+        <v>196</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AJ2" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>806</v>
+        <v>3</v>
       </c>
       <c r="AL2" s="1"/>
       <c r="AM2" s="1"/>
@@ -22680,26 +22680,20 @@
         <v>1</v>
       </c>
       <c r="AT2" s="1">
-        <v>1.2</v>
+        <v>3.15</v>
       </c>
       <c r="AU2" s="1">
-        <v>0.3</v>
+        <v>1.19</v>
       </c>
       <c r="AV2" s="1">
-        <v>4.2</v>
+        <v>8.39</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AX2" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="AY2" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="AZ2" s="1">
-        <v>60.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
       <c r="BA2" s="1" t="s">
         <v>0</v>
       </c>
@@ -22707,19 +22701,19 @@
         <v>1</v>
       </c>
       <c r="BC2" s="1">
-        <v>1.2</v>
+        <v>3.15</v>
       </c>
       <c r="BD2" s="1">
-        <v>0.3</v>
+        <v>1.19</v>
       </c>
       <c r="BE2" s="1">
-        <v>4.2</v>
+        <v>8.34</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>907</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:59" x14ac:dyDescent="0.25">
@@ -22756,8 +22750,8 @@
       <c r="K3" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>903</v>
+      <c r="L3" s="1">
+        <v>870</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>148</v>
@@ -22805,10 +22799,10 @@
         <v>39</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>917</v>
+        <v>904</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>918</v>
+        <v>905</v>
       </c>
       <c r="AD3" s="1" t="s">
         <v>9</v>
@@ -22820,10 +22814,10 @@
         <v>8</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>919</v>
+        <v>906</v>
       </c>
       <c r="AH3" s="1">
-        <v>0.20599999999999999</v>
+        <v>0.109</v>
       </c>
       <c r="AI3" s="1" t="s">
         <v>6</v>
@@ -22847,25 +22841,25 @@
         <v>1</v>
       </c>
       <c r="AT3" s="1">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AU3" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="AV3" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="AW3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="AY3" s="1">
         <v>0.5</v>
       </c>
-      <c r="AV3" s="1">
-        <v>3.4</v>
-      </c>
-      <c r="AW3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AX3" s="1">
-        <v>5.9</v>
-      </c>
-      <c r="AY3" s="1">
-        <v>0.7</v>
-      </c>
       <c r="AZ3" s="1">
-        <v>52.2</v>
+        <v>60.4</v>
       </c>
       <c r="BA3" s="1" t="s">
         <v>0</v>
@@ -22874,13 +22868,13 @@
         <v>1</v>
       </c>
       <c r="BC3" s="1">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="BD3" s="1">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="BE3" s="1">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" s="1" t="s">
         <v>0</v>
@@ -22972,10 +22966,10 @@
         <v>39</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="AD4" s="1" t="s">
         <v>9</v>
@@ -22987,13 +22981,13 @@
         <v>8</v>
       </c>
       <c r="AG4" s="1" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="AH4" s="1">
-        <v>0.318</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="AI4" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AJ4" s="1" t="s">
         <v>36</v>
@@ -23014,25 +23008,25 @@
         <v>1</v>
       </c>
       <c r="AT4" s="1">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="AU4" s="1">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AV4" s="1">
-        <v>2.2999999999999998</v>
+        <v>3.4</v>
       </c>
       <c r="AW4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX4" s="1">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY4" s="1">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AZ4" s="1">
-        <v>33.799999999999997</v>
+        <v>52.2</v>
       </c>
       <c r="BA4" s="1" t="s">
         <v>0</v>
@@ -23041,13 +23035,13 @@
         <v>1</v>
       </c>
       <c r="BC4" s="1">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="BD4" s="1">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="BE4" s="1">
-        <v>2.2999999999999998</v>
+        <v>3.4</v>
       </c>
       <c r="BF4" s="1" t="s">
         <v>0</v>
@@ -23139,10 +23133,10 @@
         <v>39</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="AD5" s="1" t="s">
         <v>9</v>
@@ -23154,13 +23148,13 @@
         <v>8</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="AH5" s="1">
-        <v>6.4000000000000001E-2</v>
+        <v>0.318</v>
       </c>
       <c r="AI5" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AJ5" s="1" t="s">
         <v>36</v>
@@ -23181,25 +23175,25 @@
         <v>1</v>
       </c>
       <c r="AT5" s="1">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="AU5" s="1">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="AV5" s="1">
-        <v>9.1999999999999993</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="AW5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX5" s="1">
-        <v>14.1</v>
+        <v>3.8</v>
       </c>
       <c r="AY5" s="1">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="AZ5" s="1">
-        <v>133</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="BA5" s="1" t="s">
         <v>0</v>
@@ -23208,13 +23202,13 @@
         <v>1</v>
       </c>
       <c r="BC5" s="1">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="BD5" s="1">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="BE5" s="1">
-        <v>9.1999999999999993</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="BF5" s="1" t="s">
         <v>0</v>
@@ -23303,13 +23297,13 @@
         <v>0</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>911</v>
+        <v>923</v>
       </c>
       <c r="AC6" s="1" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="AD6" s="1" t="s">
         <v>9</v>
@@ -23321,13 +23315,13 @@
         <v>8</v>
       </c>
       <c r="AG6" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="AH6" s="1" t="s">
-        <v>351</v>
+        <v>925</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="AI6" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AJ6" s="1" t="s">
         <v>36</v>
@@ -23348,25 +23342,25 @@
         <v>1</v>
       </c>
       <c r="AT6" s="1">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="AU6" s="1">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AV6" s="1">
-        <v>1.9</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AW6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX6" s="1">
-        <v>1.9</v>
+        <v>14.1</v>
       </c>
       <c r="AY6" s="1">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="AZ6" s="1">
-        <v>4.5</v>
+        <v>133</v>
       </c>
       <c r="BA6" s="1" t="s">
         <v>0</v>
@@ -23375,13 +23369,13 @@
         <v>1</v>
       </c>
       <c r="BC6" s="1">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="BD6" s="1">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="BE6" s="1">
-        <v>1.9</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="BF6" s="1" t="s">
         <v>0</v>
@@ -23470,13 +23464,13 @@
         <v>0</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="AD7" s="1" t="s">
         <v>9</v>
@@ -23488,10 +23482,10 @@
         <v>8</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>910</v>
+        <v>351</v>
       </c>
       <c r="AI7" s="1" t="s">
         <v>26</v>
@@ -23515,25 +23509,25 @@
         <v>1</v>
       </c>
       <c r="AT7" s="1">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AU7" s="1">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AV7" s="1">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AW7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX7" s="1">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AY7" s="1">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AZ7" s="1">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="BA7" s="1" t="s">
         <v>0</v>
@@ -23542,13 +23536,13 @@
         <v>1</v>
       </c>
       <c r="BC7" s="1">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="BD7" s="1">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="BE7" s="1">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="BF7" s="1" t="s">
         <v>0</v>
@@ -23640,10 +23634,10 @@
         <v>11</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="AC8" s="1" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="AD8" s="1" t="s">
         <v>9</v>
@@ -23655,10 +23649,10 @@
         <v>8</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>916</v>
-      </c>
-      <c r="AH8" s="1">
-        <v>0.24099999999999999</v>
+        <v>909</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>910</v>
       </c>
       <c r="AI8" s="1" t="s">
         <v>26</v>
@@ -23682,25 +23676,25 @@
         <v>1</v>
       </c>
       <c r="AT8" s="1">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AU8" s="1">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AV8" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="AW8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX8" s="1">
         <v>2.4</v>
       </c>
-      <c r="AW8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="AX8" s="1">
-        <v>2.1</v>
-      </c>
       <c r="AY8" s="1">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AZ8" s="1">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA8" s="1" t="s">
         <v>0</v>
@@ -23709,13 +23703,13 @@
         <v>1</v>
       </c>
       <c r="BC8" s="1">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BD8" s="1">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="BE8" s="1">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="BF8" s="1" t="s">
         <v>0</v>
@@ -23726,16 +23720,16 @@
     </row>
     <row r="9" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>1059</v>
+        <v>900</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1060</v>
+        <v>901</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1061</v>
+        <v>902</v>
       </c>
       <c r="D9" s="1">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="E9" s="1" t="b">
         <v>1</v>
@@ -23756,28 +23750,28 @@
         <v>20</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>1062</v>
+        <v>903</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>1062</v>
+        <v>903</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>278</v>
+        <v>148</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>1063</v>
+        <v>326</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>42</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>35</v>
@@ -23786,10 +23780,10 @@
         <v>21</v>
       </c>
       <c r="U9" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>145</v>
+        <v>14</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>53</v>
@@ -23798,34 +23792,34 @@
         <v>13</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>1064</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>1065</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>513</v>
+        <v>11</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>1072</v>
+        <v>914</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>1072</v>
+        <v>915</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="AF9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="AG9" s="1" t="s">
-        <v>1073</v>
-      </c>
-      <c r="AH9" s="1" t="s">
-        <v>1074</v>
+        <v>916</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>0.24099999999999999</v>
       </c>
       <c r="AI9" s="1" t="s">
         <v>26</v>
@@ -23834,7 +23828,7 @@
         <v>36</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>1069</v>
+        <v>806</v>
       </c>
       <c r="AL9" s="1"/>
       <c r="AM9" s="1"/>
@@ -23846,49 +23840,49 @@
         <v>35</v>
       </c>
       <c r="AS9" s="1" t="s">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="AT9" s="1">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AU9" s="1">
-        <v>1.08</v>
+        <v>0.8</v>
       </c>
       <c r="AV9" s="1">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AW9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX9" s="1">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="AY9" s="1">
-        <v>1.1000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="AZ9" s="1">
-        <v>2.08</v>
-      </c>
-      <c r="BA9" s="1">
-        <v>1.0999999999999999E-2</v>
+        <v>5.8</v>
+      </c>
+      <c r="BA9" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="BB9" s="1" t="s">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="BC9" s="1">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BD9" s="1">
-        <v>1.08</v>
+        <v>0.8</v>
       </c>
       <c r="BE9" s="1">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="BF9" s="1" t="s">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="BG9" s="1" t="s">
-        <v>1571</v>
+        <v>907</v>
       </c>
     </row>
     <row r="10" spans="1:59" x14ac:dyDescent="0.25">
@@ -23971,13 +23965,13 @@
         <v>1065</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>80</v>
+        <v>513</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>80</v>
+        <v>1072</v>
       </c>
       <c r="AD10" s="1" t="s">
         <v>112</v>
@@ -23989,10 +23983,10 @@
         <v>8</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="AH10" s="1" t="s">
-        <v>944</v>
+        <v>1074</v>
       </c>
       <c r="AI10" s="1" t="s">
         <v>26</v>
@@ -24016,43 +24010,43 @@
         <v>139</v>
       </c>
       <c r="AT10" s="1">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AU10" s="1">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AV10" s="1">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AW10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX10" s="1">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="AY10" s="1">
-        <v>0.89</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="AZ10" s="1">
-        <v>1.96</v>
-      </c>
-      <c r="BA10" s="1" t="s">
-        <v>545</v>
+        <v>2.08</v>
+      </c>
+      <c r="BA10" s="1">
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="BB10" s="1" t="s">
         <v>139</v>
       </c>
       <c r="BC10" s="1">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="BD10" s="1">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="BE10" s="1">
-        <v>2</v>
-      </c>
-      <c r="BF10" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>1.85</v>
+      </c>
+      <c r="BF10" s="1" t="s">
+        <v>1024</v>
       </c>
       <c r="BG10" s="1" t="s">
         <v>1571</v>
@@ -24138,13 +24132,13 @@
         <v>1065</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>541</v>
+        <v>80</v>
       </c>
       <c r="AD11" s="1" t="s">
         <v>112</v>
@@ -24156,10 +24150,10 @@
         <v>8</v>
       </c>
       <c r="AG11" s="1" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="AH11" s="1" t="s">
-        <v>1068</v>
+        <v>944</v>
       </c>
       <c r="AI11" s="1" t="s">
         <v>26</v>
@@ -24183,43 +24177,43 @@
         <v>139</v>
       </c>
       <c r="AT11" s="1">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AU11" s="1">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AV11" s="1">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AW11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX11" s="1">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AY11" s="1">
-        <v>1.03</v>
+        <v>0.89</v>
       </c>
       <c r="AZ11" s="1">
-        <v>2.37</v>
-      </c>
-      <c r="BA11" s="1">
-        <v>3.7999999999999999E-2</v>
+        <v>1.96</v>
+      </c>
+      <c r="BA11" s="1" t="s">
+        <v>545</v>
       </c>
       <c r="BB11" s="1" t="s">
         <v>139</v>
       </c>
       <c r="BC11" s="1">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="BD11" s="1">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="BE11" s="1">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="BF11" s="1">
-        <v>3.6999999999999998E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="BG11" s="1" t="s">
         <v>1571</v>
@@ -24227,16 +24221,16 @@
     </row>
     <row r="12" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>138</v>
+        <v>1059</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>137</v>
+        <v>1060</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>136</v>
+        <v>1061</v>
       </c>
       <c r="D12" s="1">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="E12" s="1" t="b">
         <v>1</v>
@@ -24256,41 +24250,41 @@
       <c r="J12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="1">
-        <v>2523</v>
+      <c r="K12" s="1" t="s">
+        <v>1062</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>135</v>
+        <v>1062</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>18</v>
+        <v>278</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>134</v>
+        <v>1063</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P12" t="s">
-        <v>1574</v>
+      <c r="P12" s="1" t="s">
+        <v>1575</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>1521</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="T12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="U12" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>53</v>
@@ -24298,35 +24292,35 @@
       <c r="X12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Y12" s="1">
-        <v>121</v>
-      </c>
-      <c r="Z12" s="1">
-        <v>4.8000000000000001E-2</v>
+      <c r="Y12" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>1065</v>
       </c>
       <c r="AA12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>131</v>
+        <v>1066</v>
       </c>
       <c r="AC12" s="1" t="s">
-        <v>130</v>
+        <v>541</v>
       </c>
       <c r="AD12" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="AF12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="AG12" s="1" t="s">
-        <v>0</v>
+        <v>1067</v>
       </c>
       <c r="AH12" s="1" t="s">
-        <v>0</v>
+        <v>1068</v>
       </c>
       <c r="AI12" s="1" t="s">
         <v>26</v>
@@ -24335,7 +24329,7 @@
         <v>36</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>36</v>
+        <v>1069</v>
       </c>
       <c r="AL12" s="1"/>
       <c r="AM12" s="1"/>
@@ -24344,69 +24338,75 @@
       <c r="AP12" s="1"/>
       <c r="AQ12" s="1"/>
       <c r="AR12" s="1" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="AS12" s="1" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="AT12" s="1">
-        <v>1.7430000000000001</v>
+        <v>1.42</v>
       </c>
       <c r="AU12" s="1">
-        <v>1.002</v>
+        <v>1.02</v>
       </c>
       <c r="AV12" s="1">
-        <v>3.03</v>
+        <v>1.98</v>
       </c>
       <c r="AW12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX12" s="1">
-        <v>1.7430000000000001</v>
+        <v>1.56</v>
       </c>
       <c r="AY12" s="1">
-        <v>1.002</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" s="1">
-        <v>3.03</v>
+        <v>2.37</v>
       </c>
       <c r="BA12" s="1">
-        <v>4.9000000000000002E-2</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="BB12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC12" s="1"/>
-      <c r="BD12" s="1"/>
-      <c r="BE12" s="1"/>
-      <c r="BF12" s="1" t="s">
-        <v>0</v>
+        <v>139</v>
+      </c>
+      <c r="BC12" s="1">
+        <v>1.42</v>
+      </c>
+      <c r="BD12" s="1">
+        <v>1.02</v>
+      </c>
+      <c r="BE12" s="1">
+        <v>1.98</v>
+      </c>
+      <c r="BF12" s="1">
+        <v>3.6999999999999998E-2</v>
       </c>
       <c r="BG12" s="1" t="s">
-        <v>0</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="13" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>693</v>
+        <v>138</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>694</v>
+        <v>137</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>695</v>
+        <v>136</v>
       </c>
       <c r="D13" s="1">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="E13" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>1375</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>22</v>
@@ -24417,8 +24417,8 @@
       <c r="J13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>135</v>
+      <c r="K13" s="1">
+        <v>2523</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>135</v>
@@ -24451,7 +24451,7 @@
         <v>1</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>53</v>
@@ -24459,44 +24459,44 @@
       <c r="X13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Y13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="1" t="s">
-        <v>0</v>
+      <c r="Y13" s="1">
+        <v>121</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="AA13" s="1" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="AC13" s="1" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="AF13" s="1" t="s">
-        <v>696</v>
+        <v>8</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>697</v>
+        <v>0</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>698</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AJ13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AK13" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
@@ -24508,31 +24508,31 @@
         <v>2</v>
       </c>
       <c r="AS13" s="1" t="s">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="AT13" s="1">
-        <v>1.79</v>
+        <v>1.7430000000000001</v>
       </c>
       <c r="AU13" s="1">
-        <v>1.04</v>
+        <v>1.002</v>
       </c>
       <c r="AV13" s="1">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="AW13" s="1" t="s">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="AX13" s="1">
-        <v>1.79</v>
+        <v>1.7430000000000001</v>
       </c>
       <c r="AY13" s="1">
-        <v>1.04</v>
+        <v>1.002</v>
       </c>
       <c r="AZ13" s="1">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="BA13" s="1">
-        <v>4.2999999999999997E-2</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="BB13" s="1" t="s">
         <v>0</v>
@@ -24642,13 +24642,13 @@
         <v>53</v>
       </c>
       <c r="AF14" s="1" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="AH14" s="1" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="AI14" s="1" t="s">
         <v>6</v>
@@ -24672,28 +24672,28 @@
         <v>139</v>
       </c>
       <c r="AT14" s="1">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="AU14" s="1">
-        <v>0.86</v>
+        <v>1.04</v>
       </c>
       <c r="AV14" s="1">
-        <v>2.29</v>
+        <v>3.08</v>
       </c>
       <c r="AW14" s="1" t="s">
         <v>139</v>
       </c>
       <c r="AX14" s="1">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="AY14" s="1">
-        <v>0.86</v>
+        <v>1.04</v>
       </c>
       <c r="AZ14" s="1">
-        <v>2.29</v>
-      </c>
-      <c r="BA14" s="1" t="s">
-        <v>702</v>
+        <v>3.08</v>
+      </c>
+      <c r="BA14" s="1">
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="BB14" s="1" t="s">
         <v>0</v>
@@ -24803,13 +24803,13 @@
         <v>53</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>160</v>
+        <v>699</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="AH15" s="1" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="AI15" s="1" t="s">
         <v>6</v>
@@ -24833,28 +24833,28 @@
         <v>139</v>
       </c>
       <c r="AT15" s="1">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AU15" s="1">
-        <v>0.94</v>
+        <v>0.86</v>
       </c>
       <c r="AV15" s="1">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="AW15" s="1" t="s">
         <v>139</v>
       </c>
       <c r="AX15" s="1">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AY15" s="1">
-        <v>0.94</v>
+        <v>0.86</v>
       </c>
       <c r="AZ15" s="1">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="BA15" s="1" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="BB15" s="1" t="s">
         <v>0</v>
@@ -24964,16 +24964,16 @@
         <v>53</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>706</v>
+        <v>160</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="AH16" s="1" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="AI16" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AJ16" s="1" t="s">
         <v>36</v>
@@ -24994,28 +24994,28 @@
         <v>139</v>
       </c>
       <c r="AT16" s="1">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AU16" s="1">
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="AV16" s="1">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="AW16" s="1" t="s">
         <v>139</v>
       </c>
       <c r="AX16" s="1">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AY16" s="1">
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="AZ16" s="1">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="BA16" s="1" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="BB16" s="1" t="s">
         <v>0</v>
@@ -25125,16 +25125,16 @@
         <v>53</v>
       </c>
       <c r="AF17" s="1" t="s">
-        <v>74</v>
+        <v>706</v>
       </c>
       <c r="AG17" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="AH17" s="1">
-        <v>7.8874356000000007E-2</v>
+        <v>707</v>
+      </c>
+      <c r="AH17" s="1" t="s">
+        <v>708</v>
       </c>
       <c r="AI17" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AJ17" s="1" t="s">
         <v>36</v>
@@ -25155,28 +25155,28 @@
         <v>139</v>
       </c>
       <c r="AT17" s="1">
-        <v>1.82</v>
+        <v>1.26</v>
       </c>
       <c r="AU17" s="1">
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
       <c r="AV17" s="1">
-        <v>3.16</v>
+        <v>1.64</v>
       </c>
       <c r="AW17" s="1" t="s">
         <v>139</v>
       </c>
       <c r="AX17" s="1">
-        <v>1.82</v>
+        <v>1.26</v>
       </c>
       <c r="AY17" s="1">
-        <v>1.05</v>
+        <v>0.97</v>
       </c>
       <c r="AZ17" s="1">
-        <v>3.16</v>
-      </c>
-      <c r="BA17" s="1">
-        <v>3.5999999999999997E-2</v>
+        <v>1.64</v>
+      </c>
+      <c r="BA17" s="1" t="s">
+        <v>709</v>
       </c>
       <c r="BB17" s="1" t="s">
         <v>0</v>
@@ -25193,13 +25193,13 @@
     </row>
     <row r="18" spans="1:357" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>1045</v>
+        <v>693</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1046</v>
+        <v>694</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1047</v>
+        <v>695</v>
       </c>
       <c r="D18" s="1">
         <v>2017</v>
@@ -25211,7 +25211,7 @@
         <v>1375</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>22</v>
@@ -25222,11 +25222,11 @@
       <c r="J18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K18" s="1">
-        <v>4245</v>
-      </c>
-      <c r="L18" s="1">
-        <v>4245</v>
+      <c r="K18" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>18</v>
@@ -25256,7 +25256,7 @@
         <v>1</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>53</v>
@@ -25264,44 +25264,44 @@
       <c r="X18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Y18" s="16">
-        <v>225</v>
-      </c>
-      <c r="Z18" s="1">
-        <v>5.2999999999999999E-2</v>
+      <c r="Y18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="AA18" s="1" t="s">
         <v>80</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>1048</v>
+        <v>80</v>
       </c>
       <c r="AC18" s="1" t="s">
         <v>80</v>
       </c>
       <c r="AD18" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="AF18" s="1" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="1" t="s">
-        <v>0</v>
+        <v>710</v>
+      </c>
+      <c r="AH18" s="1">
+        <v>7.8874356000000007E-2</v>
       </c>
       <c r="AI18" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AJ18" s="1" t="s">
         <v>36</v>
       </c>
       <c r="AK18" s="1" t="s">
-        <v>806</v>
+        <v>56</v>
       </c>
       <c r="AL18" s="1"/>
       <c r="AM18" s="1"/>
@@ -25313,31 +25313,31 @@
         <v>2</v>
       </c>
       <c r="AS18" s="1" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="AT18" s="1">
-        <v>1.085</v>
+        <v>1.82</v>
       </c>
       <c r="AU18" s="1">
-        <v>0.73199999999999998</v>
+        <v>1.05</v>
       </c>
       <c r="AV18" s="1">
-        <v>1.609</v>
+        <v>3.16</v>
       </c>
       <c r="AW18" s="1" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="AX18" s="1">
-        <v>1.085</v>
+        <v>1.82</v>
       </c>
       <c r="AY18" s="1">
-        <v>0.73199999999999998</v>
+        <v>1.05</v>
       </c>
       <c r="AZ18" s="1">
-        <v>1.609</v>
-      </c>
-      <c r="BA18" s="1" t="s">
-        <v>1049</v>
+        <v>3.16</v>
+      </c>
+      <c r="BA18" s="1">
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="BB18" s="1" t="s">
         <v>0</v>
@@ -25432,13 +25432,13 @@
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="AA19" s="1" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="AC19" s="1" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="AD19" s="1" t="s">
         <v>9</v>
@@ -25477,28 +25477,28 @@
         <v>1</v>
       </c>
       <c r="AT19" s="1">
-        <v>1.5409999999999999</v>
+        <v>1.085</v>
       </c>
       <c r="AU19" s="1">
-        <v>1.0489999999999999</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="AV19" s="1">
-        <v>2.2599999999999998</v>
+        <v>1.609</v>
       </c>
       <c r="AW19" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX19" s="1">
-        <v>1.5409999999999999</v>
+        <v>1.085</v>
       </c>
       <c r="AY19" s="1">
-        <v>1.0489999999999999</v>
+        <v>0.73199999999999998</v>
       </c>
       <c r="AZ19" s="1">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="BA19" s="1">
-        <v>2.8000000000000001E-2</v>
+        <v>1.609</v>
+      </c>
+      <c r="BA19" s="1" t="s">
+        <v>1049</v>
       </c>
       <c r="BB19" s="1" t="s">
         <v>0</v>
@@ -25515,22 +25515,22 @@
     </row>
     <row r="20" spans="1:357" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>1075</v>
+        <v>1045</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1076</v>
+        <v>1046</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1077</v>
+        <v>1047</v>
       </c>
       <c r="D20" s="1">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="E20" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>1375</v>
@@ -25544,26 +25544,26 @@
       <c r="J20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>1078</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>1078</v>
+      <c r="K20" s="1">
+        <v>4245</v>
+      </c>
+      <c r="L20" s="1">
+        <v>4245</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>1079</v>
+        <v>134</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>42</v>
       </c>
       <c r="P20" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>1521</v>
@@ -25578,7 +25578,7 @@
         <v>1</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>53</v>
@@ -25586,35 +25586,35 @@
       <c r="X20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Y20" s="1">
-        <v>72</v>
+      <c r="Y20" s="16">
+        <v>225</v>
       </c>
       <c r="Z20" s="1">
-        <v>3.2000000000000001E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="AA20" s="1" t="s">
         <v>11</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>1080</v>
+        <v>1050</v>
       </c>
       <c r="AC20" s="1" t="s">
-        <v>1080</v>
+        <v>11</v>
       </c>
       <c r="AD20" s="1" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="AF20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>1081</v>
-      </c>
-      <c r="AH20" s="1">
-        <v>1.2702445E-2</v>
+        <v>0</v>
+      </c>
+      <c r="AH20" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="AI20" s="1" t="s">
         <v>26</v>
@@ -25623,7 +25623,7 @@
         <v>36</v>
       </c>
       <c r="AK20" s="1" t="s">
-        <v>1069</v>
+        <v>806</v>
       </c>
       <c r="AL20" s="1"/>
       <c r="AM20" s="1"/>
@@ -25638,28 +25638,28 @@
         <v>1</v>
       </c>
       <c r="AT20" s="1">
-        <v>4.4800000000000004</v>
+        <v>1.5409999999999999</v>
       </c>
       <c r="AU20" s="1">
-        <v>1.72</v>
+        <v>1.0489999999999999</v>
       </c>
       <c r="AV20" s="1">
-        <v>11.7</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="AW20" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX20" s="1">
-        <v>4.4800000000000004</v>
+        <v>1.5409999999999999</v>
       </c>
       <c r="AY20" s="1">
-        <v>1.72</v>
+        <v>1.0489999999999999</v>
       </c>
       <c r="AZ20" s="1">
-        <v>11.7</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="BA20" s="1">
-        <v>2E-3</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="BB20" s="1" t="s">
         <v>0</v>
@@ -25747,8 +25747,8 @@
       <c r="X21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Y21" s="1" t="s">
-        <v>453</v>
+      <c r="Y21" s="1">
+        <v>72</v>
       </c>
       <c r="Z21" s="1">
         <v>3.2000000000000001E-2</v>
@@ -25757,10 +25757,10 @@
         <v>11</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>541</v>
+        <v>1080</v>
       </c>
       <c r="AC21" s="1" t="s">
-        <v>541</v>
+        <v>1080</v>
       </c>
       <c r="AD21" s="1" t="s">
         <v>67</v>
@@ -25772,10 +25772,10 @@
         <v>8</v>
       </c>
       <c r="AG21" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="AH21" s="1">
-        <v>1.3337567E-2</v>
+        <v>1.2702445E-2</v>
       </c>
       <c r="AI21" s="1" t="s">
         <v>26</v>
@@ -25799,28 +25799,28 @@
         <v>1</v>
       </c>
       <c r="AT21" s="1">
-        <v>5.28</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="AU21" s="1">
-        <v>2.17</v>
+        <v>1.72</v>
       </c>
       <c r="AV21" s="1">
-        <v>12.84</v>
+        <v>11.7</v>
       </c>
       <c r="AW21" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX21" s="1">
-        <v>5.28</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="AY21" s="1">
-        <v>2.17</v>
+        <v>1.72</v>
       </c>
       <c r="AZ21" s="1">
-        <v>12.84</v>
-      </c>
-      <c r="BA21" s="1" t="s">
-        <v>60</v>
+        <v>11.7</v>
+      </c>
+      <c r="BA21" s="1">
+        <v>2E-3</v>
       </c>
       <c r="BB21" s="1" t="s">
         <v>0</v>
@@ -26135,16 +26135,16 @@
     </row>
     <row r="22" spans="1:357" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>1432</v>
+        <v>1075</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>230</v>
+        <v>1076</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>229</v>
+        <v>1077</v>
       </c>
       <c r="D22" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E22" s="1" t="b">
         <v>0</v>
@@ -26165,16 +26165,16 @@
         <v>20</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>228</v>
+        <v>1078</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>228</v>
+        <v>1078</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>18</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>43</v>
+        <v>1079</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>42</v>
@@ -26183,7 +26183,7 @@
         <v>1575</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>15</v>
+        <v>258</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>1521</v>
@@ -26198,7 +26198,7 @@
         <v>1</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>53</v>
@@ -26207,23 +26207,22 @@
         <v>13</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>227</v>
+        <v>453</v>
       </c>
       <c r="Z22" s="1">
-        <f>Table1[[#This Row],[hiv_num]]/Table1[[#This Row],[analytical_sample_size]]</f>
-        <v>0.24390243902439024</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="AA22" s="1" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>233</v>
+        <v>541</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>232</v>
+        <v>541</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="AE22" s="1" t="s">
         <v>53</v>
@@ -26232,11 +26231,10 @@
         <v>8</v>
       </c>
       <c r="AG22" s="1" t="s">
-        <v>231</v>
+        <v>1082</v>
       </c>
       <c r="AH22" s="1">
-        <f>232/(232+1716)</f>
-        <v>0.11909650924024641</v>
+        <v>1.3337567E-2</v>
       </c>
       <c r="AI22" s="1" t="s">
         <v>26</v>
@@ -26245,7 +26243,7 @@
         <v>36</v>
       </c>
       <c r="AK22" s="1" t="s">
-        <v>224</v>
+        <v>1069</v>
       </c>
       <c r="AL22" s="1"/>
       <c r="AM22" s="1"/>
@@ -26260,28 +26258,28 @@
         <v>1</v>
       </c>
       <c r="AT22" s="1">
-        <v>0.65</v>
+        <v>5.28</v>
       </c>
       <c r="AU22" s="1">
-        <v>0.41</v>
+        <v>2.17</v>
       </c>
       <c r="AV22" s="1">
-        <v>1.03</v>
+        <v>12.84</v>
       </c>
       <c r="AW22" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX22" s="1">
-        <v>0.65</v>
+        <v>5.28</v>
       </c>
       <c r="AY22" s="1">
-        <v>0.41</v>
+        <v>2.17</v>
       </c>
       <c r="AZ22" s="1">
-        <v>1.03</v>
-      </c>
-      <c r="BA22" s="1">
-        <v>6.7000000000000004E-2</v>
+        <v>12.84</v>
+      </c>
+      <c r="BA22" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="BB22" s="1" t="s">
         <v>0</v>
@@ -26675,13 +26673,13 @@
         <v>0.24390243902439024</v>
       </c>
       <c r="AA23" s="1" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="AC23" s="1" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="AD23" s="1" t="s">
         <v>14</v>
@@ -26693,11 +26691,11 @@
         <v>8</v>
       </c>
       <c r="AG23" s="1" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="AH23" s="1">
-        <f>202/(202+1747)</f>
-        <v>0.10364289379168805</v>
+        <f>232/(232+1716)</f>
+        <v>0.11909650924024641</v>
       </c>
       <c r="AI23" s="1" t="s">
         <v>26</v>
@@ -26721,28 +26719,28 @@
         <v>1</v>
       </c>
       <c r="AT23" s="1">
-        <v>1.06</v>
+        <v>0.65</v>
       </c>
       <c r="AU23" s="1">
-        <v>0.69</v>
+        <v>0.41</v>
       </c>
       <c r="AV23" s="1">
-        <v>1.61</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX23" s="1">
-        <v>1.06</v>
+        <v>0.65</v>
       </c>
       <c r="AY23" s="1">
-        <v>0.69</v>
+        <v>0.41</v>
       </c>
       <c r="AZ23" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="BA23" s="1" t="s">
-        <v>223</v>
+        <v>1.03</v>
+      </c>
+      <c r="BA23" s="1">
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="BB23" s="1" t="s">
         <v>0</v>
@@ -27057,22 +27055,22 @@
     </row>
     <row r="24" spans="1:357" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>46</v>
+        <v>1432</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>45</v>
+        <v>230</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>44</v>
+        <v>229</v>
       </c>
       <c r="D24" s="1">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="E24" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>1375</v>
@@ -27086,11 +27084,11 @@
       <c r="J24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K24" s="1">
-        <v>1817</v>
+      <c r="K24" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>40</v>
+        <v>228</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>18</v>
@@ -27111,13 +27109,13 @@
         <v>1521</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="T24" s="1" t="s">
         <v>21</v>
       </c>
       <c r="U24" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V24" s="1" t="s">
         <v>41</v>
@@ -27129,104 +27127,93 @@
         <v>13</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z24" s="1" t="s">
-        <v>13</v>
+        <v>227</v>
+      </c>
+      <c r="Z24" s="1">
+        <f>Table1[[#This Row],[hiv_num]]/Table1[[#This Row],[analytical_sample_size]]</f>
+        <v>0.24390243902439024</v>
       </c>
       <c r="AA24" s="1" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>38</v>
+        <v>226</v>
       </c>
       <c r="AC24" s="1" t="s">
-        <v>51</v>
+        <v>226</v>
       </c>
       <c r="AD24" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AE24" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="AF24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AG24" s="1">
-        <v>1098</v>
+      <c r="AG24" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="AH24" s="1">
-        <f>1098/1817</f>
-        <v>0.60429279031370386</v>
+        <f>202/(202+1747)</f>
+        <v>0.10364289379168805</v>
       </c>
       <c r="AI24" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AJ24" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AK24" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AL24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AM24" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AN24" s="1" t="s">
-        <v>26</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="AL24" s="1"/>
+      <c r="AM24" s="1"/>
+      <c r="AN24" s="1"/>
       <c r="AO24" s="1"/>
       <c r="AP24" s="1"/>
       <c r="AQ24" s="1"/>
       <c r="AR24" s="1" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="AS24" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AT24" s="1">
-        <v>0.49</v>
+        <v>1.06</v>
       </c>
       <c r="AU24" s="1">
-        <v>0.13</v>
+        <v>0.69</v>
       </c>
       <c r="AV24" s="1">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AW24" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX24" s="1">
-        <v>0.59</v>
+        <v>1.06</v>
       </c>
       <c r="AY24" s="1">
-        <v>0.2</v>
+        <v>0.69</v>
       </c>
       <c r="AZ24" s="1">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="BA24" s="1" t="s">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="BB24" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BC24" s="1">
-        <v>0.49</v>
-      </c>
-      <c r="BD24" s="1">
-        <v>0.13</v>
-      </c>
-      <c r="BE24" s="1">
-        <v>1.82</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BC24" s="1"/>
+      <c r="BD24" s="1"/>
+      <c r="BE24" s="1"/>
       <c r="BF24" s="1" t="s">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="BG24" s="1" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="BH24"/>
       <c r="BI24"/>
@@ -27562,7 +27549,7 @@
         <v>1817</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>18</v>
@@ -27601,10 +27588,10 @@
         <v>13</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="AA25" s="1" t="s">
         <v>39</v>
@@ -27613,7 +27600,7 @@
         <v>38</v>
       </c>
       <c r="AC25" s="1" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="AD25" s="1" t="s">
         <v>9</v>
@@ -27632,24 +27619,26 @@
         <v>0.60429279031370386</v>
       </c>
       <c r="AI25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AK25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AM25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AN25" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AJ25" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK25" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AL25" s="1"/>
-      <c r="AM25" s="1"/>
-      <c r="AN25" s="1"/>
       <c r="AO25" s="1"/>
-      <c r="AP25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AQ25" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="AP25" s="1"/>
+      <c r="AQ25" s="1"/>
       <c r="AR25" s="1" t="s">
         <v>35</v>
       </c>
@@ -27657,25 +27646,25 @@
         <v>1</v>
       </c>
       <c r="AT25" s="1">
-        <v>0.92</v>
+        <v>0.49</v>
       </c>
       <c r="AU25" s="1">
-        <v>0.71</v>
+        <v>0.13</v>
       </c>
       <c r="AV25" s="1">
-        <v>1.19</v>
+        <v>1.82</v>
       </c>
       <c r="AW25" s="1" t="s">
         <v>0</v>
       </c>
       <c r="AX25" s="1">
-        <v>0.83</v>
+        <v>0.59</v>
       </c>
       <c r="AY25" s="1">
-        <v>0.66</v>
+        <v>0.2</v>
       </c>
       <c r="AZ25" s="1">
-        <v>1.05</v>
+        <v>1.72</v>
       </c>
       <c r="BA25" s="1" t="s">
         <v>0</v>
@@ -27684,16 +27673,16 @@
         <v>1</v>
       </c>
       <c r="BC25" s="1">
-        <v>0.92</v>
+        <v>0.49</v>
       </c>
       <c r="BD25" s="1">
-        <v>0.71</v>
+        <v>0.13</v>
       </c>
       <c r="BE25" s="1">
-        <v>1.19</v>
+        <v>1.82</v>
       </c>
       <c r="BF25" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="BG25" s="1" t="s">
         <v>33</v>
@@ -27701,13 +27690,13 @@
     </row>
     <row r="26" spans="1:357" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>449</v>
+        <v>46</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>450</v>
+        <v>45</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>451</v>
+        <v>44</v>
       </c>
       <c r="D26" s="1">
         <v>2016</v>
@@ -27725,46 +27714,46 @@
         <v>22</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>452</v>
+        <v>21</v>
       </c>
       <c r="J26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K26" s="1">
-        <v>72</v>
+        <v>1817</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>453</v>
+        <v>58</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>260</v>
+        <v>18</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>454</v>
+        <v>43</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>455</v>
+        <v>42</v>
       </c>
       <c r="P26" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>1521</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>1523</v>
+        <v>21</v>
       </c>
       <c r="U26" s="1">
         <v>2</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="W26" s="1" t="s">
         <v>53</v>
@@ -27773,104 +27762,113 @@
         <v>13</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>453</v>
+        <v>57</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="AA26" s="1" t="s">
         <v>39</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>456</v>
+        <v>38</v>
       </c>
       <c r="AC26" s="1" t="s">
-        <v>457</v>
+        <v>37</v>
       </c>
       <c r="AD26" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AE26" s="1" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="AF26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AG26" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="AH26" s="1" t="s">
-        <v>459</v>
+        <v>8</v>
+      </c>
+      <c r="AG26" s="1">
+        <v>1098</v>
+      </c>
+      <c r="AH26" s="1">
+        <f>1098/1817</f>
+        <v>0.60429279031370386</v>
       </c>
       <c r="AI26" s="1" t="s">
         <v>26</v>
       </c>
       <c r="AJ26" s="1" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="AK26" s="1" t="s">
-        <v>460</v>
+        <v>55</v>
       </c>
       <c r="AL26" s="1"/>
       <c r="AM26" s="1"/>
       <c r="AN26" s="1"/>
-      <c r="AO26" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="AP26" s="1"/>
-      <c r="AQ26" s="1"/>
+      <c r="AO26" s="1"/>
+      <c r="AP26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AQ26" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="AR26" s="1" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="AS26" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AT26" s="1">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="AU26" s="1">
-        <v>0.2</v>
+        <v>0.71</v>
       </c>
       <c r="AV26" s="1">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AW26" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX26" s="1">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="AY26" s="1">
-        <v>0.2</v>
+        <v>0.66</v>
       </c>
       <c r="AZ26" s="1">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
       <c r="BA26" s="1" t="s">
         <v>0</v>
       </c>
       <c r="BB26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC26" s="1"/>
-      <c r="BD26" s="1"/>
-      <c r="BE26" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="BC26" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="BD26" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="BE26" s="1">
+        <v>1.19</v>
+      </c>
       <c r="BF26" s="1" t="s">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="BG26" s="1" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:357" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>518</v>
+        <v>449</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>519</v>
+        <v>450</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>483</v>
+        <v>451</v>
       </c>
       <c r="D27" s="1">
         <v>2016</v>
@@ -27894,10 +27892,10 @@
         <v>20</v>
       </c>
       <c r="K27" s="1">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>78</v>
+        <v>453</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>260</v>
@@ -27936,7 +27934,7 @@
         <v>13</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>78</v>
+        <v>453</v>
       </c>
       <c r="Z27" s="1" t="s">
         <v>13</v>
@@ -27945,7 +27943,7 @@
         <v>39</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>520</v>
+        <v>456</v>
       </c>
       <c r="AC27" s="1" t="s">
         <v>457</v>
@@ -27960,30 +27958,26 @@
         <v>63</v>
       </c>
       <c r="AG27" s="1" t="s">
-        <v>521</v>
+        <v>458</v>
       </c>
       <c r="AH27" s="1" t="s">
-        <v>522</v>
+        <v>459</v>
       </c>
       <c r="AI27" s="1" t="s">
         <v>26</v>
       </c>
       <c r="AJ27" s="1" t="s">
-        <v>523</v>
+        <v>5</v>
       </c>
       <c r="AK27" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="AL27" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="AM27" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="AN27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO27" s="1"/>
+        <v>460</v>
+      </c>
+      <c r="AL27" s="1"/>
+      <c r="AM27" s="1"/>
+      <c r="AN27" s="1"/>
+      <c r="AO27" s="1" t="s">
+        <v>461</v>
+      </c>
       <c r="AP27" s="1"/>
       <c r="AQ27" s="1"/>
       <c r="AR27" s="1" t="s">
@@ -27993,28 +27987,28 @@
         <v>1</v>
       </c>
       <c r="AT27" s="1">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="AU27" s="1">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="AV27" s="1">
-        <v>3.03</v>
+        <v>1.23</v>
       </c>
       <c r="AW27" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX27" s="1">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="AY27" s="1">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="AZ27" s="1">
-        <v>3.03</v>
-      </c>
-      <c r="BA27" s="1">
-        <v>0.64800000000000002</v>
+        <v>1.23</v>
+      </c>
+      <c r="BA27" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="BB27" s="1" t="s">
         <v>0</v>
@@ -28031,43 +28025,43 @@
     </row>
     <row r="28" spans="1:357" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>928</v>
+        <v>518</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>929</v>
+        <v>519</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>930</v>
+        <v>483</v>
       </c>
       <c r="D28" s="1">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="E28" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>21</v>
+        <v>452</v>
       </c>
       <c r="J28" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K28" s="1">
-        <v>259</v>
+        <v>74</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>931</v>
+        <v>78</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>148</v>
+        <v>260</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>454</v>
@@ -28082,40 +28076,40 @@
         <v>133</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>2</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>21</v>
+        <v>1523</v>
       </c>
       <c r="U28" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="X28" s="1" t="s">
         <v>13</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>528</v>
+        <v>78</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>932</v>
+        <v>13</v>
       </c>
       <c r="AA28" s="1" t="s">
         <v>39</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>933</v>
+        <v>520</v>
       </c>
       <c r="AC28" s="1" t="s">
-        <v>934</v>
+        <v>457</v>
       </c>
       <c r="AD28" s="1" t="s">
         <v>14</v>
@@ -28127,23 +28121,29 @@
         <v>63</v>
       </c>
       <c r="AG28" s="1" t="s">
-        <v>640</v>
+        <v>521</v>
       </c>
       <c r="AH28" s="1" t="s">
-        <v>935</v>
+        <v>522</v>
       </c>
       <c r="AI28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="AJ28" s="1" t="s">
-        <v>36</v>
+        <v>523</v>
       </c>
       <c r="AK28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL28" s="1"/>
-      <c r="AM28" s="1"/>
-      <c r="AN28" s="1"/>
+        <v>524</v>
+      </c>
+      <c r="AL28" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="AM28" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="AN28" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="AO28" s="1"/>
       <c r="AP28" s="1"/>
       <c r="AQ28" s="1"/>
@@ -28154,28 +28154,28 @@
         <v>1</v>
       </c>
       <c r="AT28" s="1">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="AU28" s="1">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="AV28" s="1">
-        <v>1.46</v>
+        <v>3.03</v>
       </c>
       <c r="AW28" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX28" s="1">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="AY28" s="1">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="AZ28" s="1">
-        <v>1.46</v>
-      </c>
-      <c r="BA28" s="1" t="s">
-        <v>0</v>
+        <v>3.03</v>
+      </c>
+      <c r="BA28" s="1">
+        <v>0.64800000000000002</v>
       </c>
       <c r="BB28" s="1" t="s">
         <v>0</v>
@@ -28192,16 +28192,16 @@
     </row>
     <row r="29" spans="1:357" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>1184</v>
+        <v>928</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>1185</v>
+        <v>929</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1186</v>
+        <v>930</v>
       </c>
       <c r="D29" s="1">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="E29" s="1" t="b">
         <v>0</v>
@@ -28210,7 +28210,7 @@
         <v>1376</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>22</v>
@@ -28221,26 +28221,26 @@
       <c r="J29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>1187</v>
+      <c r="K29" s="1">
+        <v>259</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>1187</v>
+        <v>931</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>148</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>1188</v>
+        <v>454</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>1189</v>
+        <v>455</v>
       </c>
       <c r="P29" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="R29" s="1" t="s">
         <v>1522</v>
@@ -28255,63 +28255,59 @@
         <v>0</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="X29" s="1" t="s">
         <v>13</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>0</v>
+        <v>528</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>0</v>
+        <v>932</v>
       </c>
       <c r="AA29" s="1" t="s">
         <v>39</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>1190</v>
+        <v>933</v>
       </c>
       <c r="AC29" s="1" t="s">
-        <v>761</v>
+        <v>934</v>
       </c>
       <c r="AD29" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AE29" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="AF29" s="1" t="s">
         <v>63</v>
       </c>
       <c r="AG29" s="1" t="s">
-        <v>272</v>
+        <v>640</v>
       </c>
       <c r="AH29" s="1" t="s">
-        <v>1191</v>
+        <v>935</v>
       </c>
       <c r="AI29" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AJ29" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="AK29" s="1" t="s">
-        <v>1192</v>
+        <v>0</v>
       </c>
       <c r="AL29" s="1"/>
       <c r="AM29" s="1"/>
       <c r="AN29" s="1"/>
       <c r="AO29" s="1"/>
-      <c r="AP29" s="1" t="s">
-        <v>1193</v>
-      </c>
-      <c r="AQ29" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="AP29" s="1"/>
+      <c r="AQ29" s="1"/>
       <c r="AR29" s="1" t="s">
         <v>2</v>
       </c>
@@ -28319,28 +28315,28 @@
         <v>1</v>
       </c>
       <c r="AT29" s="1">
-        <v>2.83</v>
+        <v>0.62</v>
       </c>
       <c r="AU29" s="1">
-        <v>1.65</v>
+        <v>0.27</v>
       </c>
       <c r="AV29" s="1">
-        <v>4.84</v>
+        <v>1.46</v>
       </c>
       <c r="AW29" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX29" s="1">
-        <v>2.83</v>
+        <v>0.62</v>
       </c>
       <c r="AY29" s="1">
-        <v>1.65</v>
+        <v>0.27</v>
       </c>
       <c r="AZ29" s="1">
-        <v>4.84</v>
+        <v>1.46</v>
       </c>
       <c r="BA29" s="1" t="s">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BB29" s="1" t="s">
         <v>0</v>
@@ -28357,22 +28353,22 @@
     </row>
     <row r="30" spans="1:357" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>1208</v>
+        <v>1184</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>1209</v>
+        <v>1185</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1210</v>
+        <v>1186</v>
       </c>
       <c r="D30" s="1">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="E30" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>1375</v>
@@ -28386,11 +28382,11 @@
       <c r="J30" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K30" s="1">
-        <v>1022</v>
-      </c>
-      <c r="L30" s="1">
-        <v>937</v>
+      <c r="K30" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>1187</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>148</v>
@@ -28399,7 +28395,7 @@
         <v>1188</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>1212</v>
+        <v>1189</v>
       </c>
       <c r="P30" t="s">
         <v>1574</v>
@@ -28411,16 +28407,16 @@
         <v>1522</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>21</v>
       </c>
       <c r="U30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="W30" s="1" t="s">
         <v>53</v>
@@ -28435,13 +28431,13 @@
         <v>0</v>
       </c>
       <c r="AA30" s="1" t="s">
-        <v>513</v>
+        <v>39</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>1223</v>
+        <v>1190</v>
       </c>
       <c r="AC30" s="1" t="s">
-        <v>1224</v>
+        <v>761</v>
       </c>
       <c r="AD30" s="1" t="s">
         <v>9</v>
@@ -28453,29 +28449,29 @@
         <v>63</v>
       </c>
       <c r="AG30" s="1" t="s">
-        <v>1225</v>
+        <v>272</v>
       </c>
       <c r="AH30" s="1" t="s">
-        <v>1226</v>
+        <v>1191</v>
       </c>
       <c r="AI30" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AJ30" s="1" t="s">
         <v>56</v>
       </c>
       <c r="AK30" s="1" t="s">
-        <v>721</v>
+        <v>1192</v>
       </c>
       <c r="AL30" s="1"/>
       <c r="AM30" s="1"/>
       <c r="AN30" s="1"/>
       <c r="AO30" s="1"/>
       <c r="AP30" s="1" t="s">
-        <v>9</v>
+        <v>1193</v>
       </c>
       <c r="AQ30" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="AR30" s="1" t="s">
         <v>2</v>
@@ -28484,28 +28480,28 @@
         <v>1</v>
       </c>
       <c r="AT30" s="1">
-        <v>1.1200000000000001</v>
+        <v>2.83</v>
       </c>
       <c r="AU30" s="1">
-        <v>0.87</v>
+        <v>1.65</v>
       </c>
       <c r="AV30" s="1">
-        <v>1.46</v>
+        <v>4.84</v>
       </c>
       <c r="AW30" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX30" s="1">
-        <v>1.1200000000000001</v>
+        <v>2.83</v>
       </c>
       <c r="AY30" s="1">
-        <v>0.87</v>
+        <v>1.65</v>
       </c>
       <c r="AZ30" s="1">
-        <v>1.46</v>
+        <v>4.84</v>
       </c>
       <c r="BA30" s="1" t="s">
-        <v>1227</v>
+        <v>60</v>
       </c>
       <c r="BB30" s="1" t="s">
         <v>0</v>
@@ -28555,7 +28551,7 @@
         <v>1022</v>
       </c>
       <c r="L31" s="1">
-        <v>740</v>
+        <v>937</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>148</v>
@@ -28615,13 +28611,13 @@
         <v>9</v>
       </c>
       <c r="AF31" s="1" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="AG31" s="1" t="s">
-        <v>1233</v>
+        <v>1225</v>
       </c>
       <c r="AH31" s="1" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
       <c r="AI31" s="1" t="s">
         <v>26</v>
@@ -28649,28 +28645,28 @@
         <v>1</v>
       </c>
       <c r="AT31" s="1">
-        <v>0.77</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="AU31" s="1">
-        <v>0.57999999999999996</v>
+        <v>0.87</v>
       </c>
       <c r="AV31" s="1">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="AW31" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX31" s="1">
-        <v>0.77</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="AY31" s="1">
-        <v>0.57999999999999996</v>
+        <v>0.87</v>
       </c>
       <c r="AZ31" s="1">
-        <v>1.03</v>
-      </c>
-      <c r="BA31" s="1">
-        <v>7.6999999999999999E-2</v>
+        <v>1.46</v>
+      </c>
+      <c r="BA31" s="1" t="s">
+        <v>1227</v>
       </c>
       <c r="BB31" s="1" t="s">
         <v>0</v>
@@ -28720,7 +28716,7 @@
         <v>1022</v>
       </c>
       <c r="L32" s="1">
-        <v>937</v>
+        <v>740</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>148</v>
@@ -28741,13 +28737,13 @@
         <v>1522</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="T32" s="1" t="s">
         <v>21</v>
       </c>
       <c r="U32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="1" t="s">
         <v>145</v>
@@ -28765,13 +28761,13 @@
         <v>0</v>
       </c>
       <c r="AA32" s="1" t="s">
-        <v>39</v>
+        <v>513</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="AC32" s="1" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="AD32" s="1" t="s">
         <v>9</v>
@@ -28780,13 +28776,13 @@
         <v>9</v>
       </c>
       <c r="AF32" s="1" t="s">
-        <v>63</v>
+        <v>160</v>
       </c>
       <c r="AG32" s="1" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="AH32" s="1" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="AI32" s="1" t="s">
         <v>26</v>
@@ -28808,52 +28804,46 @@
         <v>9</v>
       </c>
       <c r="AR32" s="1" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="AS32" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AT32" s="1">
-        <v>0.98039215686274506</v>
+        <v>0.77</v>
       </c>
       <c r="AU32" s="1">
-        <v>0.74626865671641784</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AV32" s="1">
-        <v>1.2820512820512819</v>
+        <v>1.03</v>
       </c>
       <c r="AW32" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX32" s="1">
-        <v>1.05</v>
+        <v>0.77</v>
       </c>
       <c r="AY32" s="1">
-        <v>0.81</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AZ32" s="1">
-        <v>1.36</v>
-      </c>
-      <c r="BA32" s="1" t="s">
-        <v>1231</v>
+        <v>1.03</v>
+      </c>
+      <c r="BA32" s="1">
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="BB32" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BC32" s="1">
-        <v>0.98039215686274506</v>
-      </c>
-      <c r="BD32" s="1">
-        <v>0.74626865671641784</v>
-      </c>
-      <c r="BE32" s="1">
-        <v>1.2820512820512819</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BC32" s="1"/>
+      <c r="BD32" s="1"/>
+      <c r="BE32" s="1"/>
       <c r="BF32" s="1" t="s">
         <v>0</v>
       </c>
       <c r="BG32" s="1" t="s">
-        <v>1232</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:59" x14ac:dyDescent="0.25">
@@ -28890,8 +28880,8 @@
       <c r="K33" s="1">
         <v>1022</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>1211</v>
+      <c r="L33" s="1">
+        <v>937</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>148</v>
@@ -28951,13 +28941,13 @@
         <v>9</v>
       </c>
       <c r="AF33" s="1" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="AG33" s="1" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="AH33" s="1" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="AI33" s="1" t="s">
         <v>26</v>
@@ -28985,40 +28975,40 @@
         <v>1</v>
       </c>
       <c r="AT33" s="1">
-        <v>0.8</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="AU33" s="1">
-        <v>0.58823529411764708</v>
+        <v>0.74626865671641784</v>
       </c>
       <c r="AV33" s="1">
-        <v>1.0869565217391299</v>
+        <v>1.2820512820512819</v>
       </c>
       <c r="AW33" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX33" s="1">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="AY33" s="1">
-        <v>0.59</v>
+        <v>0.81</v>
       </c>
       <c r="AZ33" s="1">
-        <v>1.07</v>
+        <v>1.36</v>
       </c>
       <c r="BA33" s="1" t="s">
-        <v>935</v>
+        <v>1231</v>
       </c>
       <c r="BB33" s="1" t="s">
         <v>1</v>
       </c>
       <c r="BC33" s="1">
-        <v>0.8</v>
+        <v>0.98039215686274506</v>
       </c>
       <c r="BD33" s="1">
-        <v>0.58823529411764708</v>
+        <v>0.74626865671641784</v>
       </c>
       <c r="BE33" s="1">
-        <v>1.0869565217391299</v>
+        <v>1.2820512820512819</v>
       </c>
       <c r="BF33" s="1" t="s">
         <v>0</v>
@@ -29061,8 +29051,8 @@
       <c r="K34" s="1">
         <v>1022</v>
       </c>
-      <c r="L34" s="1">
-        <v>735</v>
+      <c r="L34" s="1" t="s">
+        <v>1211</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>148</v>
@@ -29107,13 +29097,13 @@
         <v>0</v>
       </c>
       <c r="AA34" s="1" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="AB34" s="1" t="s">
-        <v>1218</v>
+        <v>1228</v>
       </c>
       <c r="AC34" s="1" t="s">
-        <v>113</v>
+        <v>1228</v>
       </c>
       <c r="AD34" s="1" t="s">
         <v>9</v>
@@ -29122,13 +29112,13 @@
         <v>9</v>
       </c>
       <c r="AF34" s="1" t="s">
-        <v>63</v>
+        <v>160</v>
       </c>
       <c r="AG34" s="1" t="s">
-        <v>894</v>
+        <v>1235</v>
       </c>
       <c r="AH34" s="1" t="s">
-        <v>1219</v>
+        <v>1236</v>
       </c>
       <c r="AI34" s="1" t="s">
         <v>26</v>
@@ -29150,46 +29140,52 @@
         <v>9</v>
       </c>
       <c r="AR34" s="1" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="AS34" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AT34" s="1">
-        <v>1.1299999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AU34" s="1">
-        <v>0.77</v>
+        <v>0.58823529411764708</v>
       </c>
       <c r="AV34" s="1">
-        <v>1.65</v>
+        <v>1.0869565217391299</v>
       </c>
       <c r="AW34" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX34" s="1">
-        <v>1.1299999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AY34" s="1">
-        <v>0.77</v>
+        <v>0.59</v>
       </c>
       <c r="AZ34" s="1">
-        <v>1.65</v>
+        <v>1.07</v>
       </c>
       <c r="BA34" s="1" t="s">
-        <v>1220</v>
+        <v>935</v>
       </c>
       <c r="BB34" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="BC34" s="1"/>
-      <c r="BD34" s="1"/>
-      <c r="BE34" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="BC34" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="BD34" s="1">
+        <v>0.58823529411764708</v>
+      </c>
+      <c r="BE34" s="1">
+        <v>1.0869565217391299</v>
+      </c>
       <c r="BF34" s="1" t="s">
         <v>0</v>
       </c>
       <c r="BG34" s="1" t="s">
-        <v>0</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="35" spans="1:59" x14ac:dyDescent="0.25">
@@ -29287,13 +29283,13 @@
         <v>9</v>
       </c>
       <c r="AF35" s="1" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="AG35" s="1" t="s">
-        <v>870</v>
+        <v>894</v>
       </c>
       <c r="AH35" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="AI35" s="1" t="s">
         <v>26</v>
@@ -29321,28 +29317,28 @@
         <v>1</v>
       </c>
       <c r="AT35" s="1">
-        <v>0.8</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="AU35" s="1">
-        <v>0.56000000000000005</v>
+        <v>0.77</v>
       </c>
       <c r="AV35" s="1">
-        <v>1.1499999999999999</v>
+        <v>1.65</v>
       </c>
       <c r="AW35" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX35" s="1">
-        <v>0.8</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="AY35" s="1">
-        <v>0.56000000000000005</v>
+        <v>0.77</v>
       </c>
       <c r="AZ35" s="1">
-        <v>1.1499999999999999</v>
+        <v>1.65</v>
       </c>
       <c r="BA35" s="1" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="BB35" s="1" t="s">
         <v>0</v>
@@ -29392,7 +29388,7 @@
         <v>1022</v>
       </c>
       <c r="L36" s="1">
-        <v>937</v>
+        <v>735</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>148</v>
@@ -29437,13 +29433,13 @@
         <v>0</v>
       </c>
       <c r="AA36" s="1" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="AB36" s="1" t="s">
-        <v>1213</v>
+        <v>1218</v>
       </c>
       <c r="AC36" s="1" t="s">
-        <v>1214</v>
+        <v>113</v>
       </c>
       <c r="AD36" s="1" t="s">
         <v>9</v>
@@ -29452,13 +29448,13 @@
         <v>9</v>
       </c>
       <c r="AF36" s="1" t="s">
-        <v>63</v>
+        <v>160</v>
       </c>
       <c r="AG36" s="1" t="s">
-        <v>496</v>
+        <v>870</v>
       </c>
       <c r="AH36" s="1" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="AI36" s="1" t="s">
         <v>26</v>
@@ -29486,28 +29482,28 @@
         <v>1</v>
       </c>
       <c r="AT36" s="1">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="AU36" s="1">
-        <v>0.45</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="AV36" s="1">
-        <v>0.95</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AW36" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX36" s="1">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="AY36" s="1">
-        <v>0.45</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="AZ36" s="1">
-        <v>0.95</v>
-      </c>
-      <c r="BA36" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="BA36" s="1" t="s">
+        <v>1222</v>
       </c>
       <c r="BB36" s="1" t="s">
         <v>0</v>
@@ -29557,7 +29553,7 @@
         <v>1022</v>
       </c>
       <c r="L37" s="1">
-        <v>739</v>
+        <v>937</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>148</v>
@@ -29617,13 +29613,13 @@
         <v>9</v>
       </c>
       <c r="AF37" s="1" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="AG37" s="1" t="s">
-        <v>1216</v>
+        <v>496</v>
       </c>
       <c r="AH37" s="1" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="AI37" s="1" t="s">
         <v>26</v>
@@ -29651,28 +29647,28 @@
         <v>1</v>
       </c>
       <c r="AT37" s="1">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="AU37" s="1">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="AV37" s="1">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="AW37" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX37" s="1">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="AY37" s="1">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="AZ37" s="1">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="BA37" s="1">
-        <v>8.9999999999999993E-3</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="BB37" s="1" t="s">
         <v>0</v>
@@ -29689,19 +29685,19 @@
     </row>
     <row r="38" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>711</v>
+        <v>1208</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>712</v>
+        <v>1209</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>713</v>
+        <v>1210</v>
       </c>
       <c r="D38" s="1">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="E38" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>1375</v>
@@ -29718,29 +29714,29 @@
       <c r="J38" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>714</v>
+      <c r="K38" s="1">
+        <v>1022</v>
       </c>
       <c r="L38" s="1">
-        <v>453</v>
+        <v>739</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>18</v>
+        <v>148</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>715</v>
+        <v>1188</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>716</v>
+        <v>1212</v>
       </c>
       <c r="P38" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>15</v>
+        <v>258</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>2</v>
@@ -29749,10 +29745,10 @@
         <v>21</v>
       </c>
       <c r="U38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="1" t="s">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="W38" s="1" t="s">
         <v>53</v>
@@ -29761,19 +29757,19 @@
         <v>13</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>717</v>
+        <v>0</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>718</v>
+        <v>0</v>
       </c>
       <c r="AA38" s="1" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="AB38" s="1" t="s">
-        <v>722</v>
+        <v>1213</v>
       </c>
       <c r="AC38" s="1" t="s">
-        <v>113</v>
+        <v>1214</v>
       </c>
       <c r="AD38" s="1" t="s">
         <v>9</v>
@@ -29782,30 +29778,33 @@
         <v>9</v>
       </c>
       <c r="AF38" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG38" s="1">
-        <v>240</v>
-      </c>
-      <c r="AH38" s="1">
-        <f>Table1[[#This Row],[exposed_num]]/453</f>
-        <v>0.5298013245033113</v>
+        <v>160</v>
+      </c>
+      <c r="AG38" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="AH38" s="1" t="s">
+        <v>1217</v>
       </c>
       <c r="AI38" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AJ38" s="1" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="AK38" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AL38" s="1"/>
       <c r="AM38" s="1"/>
       <c r="AN38" s="1"/>
       <c r="AO38" s="1"/>
-      <c r="AP38" s="1"/>
-      <c r="AQ38" s="1"/>
+      <c r="AP38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ38" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="AR38" s="1" t="s">
         <v>2</v>
       </c>
@@ -29813,28 +29812,28 @@
         <v>1</v>
       </c>
       <c r="AT38" s="1">
-        <v>1.83</v>
+        <v>0.59</v>
       </c>
       <c r="AU38" s="1">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="AV38" s="1">
-        <v>3.41</v>
+        <v>0.88</v>
       </c>
       <c r="AW38" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX38" s="1">
-        <v>1.83</v>
+        <v>0.59</v>
       </c>
       <c r="AY38" s="1">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="AZ38" s="1">
-        <v>3.41</v>
-      </c>
-      <c r="BA38" s="1" t="s">
-        <v>0</v>
+        <v>0.88</v>
+      </c>
+      <c r="BA38" s="1">
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="BB38" s="1" t="s">
         <v>0</v>
@@ -29929,13 +29928,13 @@
         <v>718</v>
       </c>
       <c r="AA39" s="1" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="AB39" s="1" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="AC39" s="1" t="s">
-        <v>541</v>
+        <v>113</v>
       </c>
       <c r="AD39" s="1" t="s">
         <v>9</v>
@@ -29947,11 +29946,11 @@
         <v>8</v>
       </c>
       <c r="AG39" s="1">
-        <v>195</v>
+        <v>240</v>
       </c>
       <c r="AH39" s="1">
         <f>Table1[[#This Row],[exposed_num]]/453</f>
-        <v>0.43046357615894038</v>
+        <v>0.5298013245033113</v>
       </c>
       <c r="AI39" s="1" t="s">
         <v>6</v>
@@ -29975,25 +29974,25 @@
         <v>1</v>
       </c>
       <c r="AT39" s="1">
-        <v>0.99</v>
+        <v>1.83</v>
       </c>
       <c r="AU39" s="1">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AV39" s="1">
-        <v>1.8</v>
+        <v>3.41</v>
       </c>
       <c r="AW39" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX39" s="1">
-        <v>0.99</v>
+        <v>1.83</v>
       </c>
       <c r="AY39" s="1">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AZ39" s="1">
-        <v>1.8</v>
+        <v>3.41</v>
       </c>
       <c r="BA39" s="1" t="s">
         <v>0</v>
@@ -30046,7 +30045,7 @@
         <v>714</v>
       </c>
       <c r="L40" s="1">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>18</v>
@@ -30091,13 +30090,13 @@
         <v>718</v>
       </c>
       <c r="AA40" s="1" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="AB40" s="1" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="AC40" s="1" t="s">
-        <v>113</v>
+        <v>541</v>
       </c>
       <c r="AD40" s="1" t="s">
         <v>9</v>
@@ -30109,31 +30108,27 @@
         <v>8</v>
       </c>
       <c r="AG40" s="1">
-        <v>247</v>
+        <v>195</v>
       </c>
       <c r="AH40" s="1">
-        <f>Table1[[#This Row],[exposed_num]]/462</f>
-        <v>0.53463203463203468</v>
+        <f>Table1[[#This Row],[exposed_num]]/453</f>
+        <v>0.43046357615894038</v>
       </c>
       <c r="AI40" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AJ40" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="AK40" s="1" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="AL40" s="1"/>
       <c r="AM40" s="1"/>
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
-      <c r="AP40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AQ40" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="AP40" s="1"/>
+      <c r="AQ40" s="1"/>
       <c r="AR40" s="1" t="s">
         <v>2</v>
       </c>
@@ -30141,25 +30136,25 @@
         <v>1</v>
       </c>
       <c r="AT40" s="1">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="AU40" s="1">
         <v>0.54</v>
       </c>
       <c r="AV40" s="1">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AW40" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX40" s="1">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="AY40" s="1">
         <v>0.54</v>
       </c>
       <c r="AZ40" s="1">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="BA40" s="1" t="s">
         <v>0</v>
@@ -30257,13 +30252,13 @@
         <v>718</v>
       </c>
       <c r="AA41" s="1" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="AB41" s="1" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="AC41" s="1" t="s">
-        <v>541</v>
+        <v>113</v>
       </c>
       <c r="AD41" s="1" t="s">
         <v>9</v>
@@ -30275,11 +30270,11 @@
         <v>8</v>
       </c>
       <c r="AG41" s="1">
-        <v>200</v>
+        <v>247</v>
       </c>
       <c r="AH41" s="1">
         <f>Table1[[#This Row],[exposed_num]]/462</f>
-        <v>0.4329004329004329</v>
+        <v>0.53463203463203468</v>
       </c>
       <c r="AI41" s="1" t="s">
         <v>26</v>
@@ -30288,7 +30283,7 @@
         <v>56</v>
       </c>
       <c r="AK41" s="1" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="AL41" s="1"/>
       <c r="AM41" s="1"/>
@@ -30307,25 +30302,25 @@
         <v>1</v>
       </c>
       <c r="AT41" s="1">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AU41" s="1">
-        <v>0.78</v>
+        <v>0.54</v>
       </c>
       <c r="AV41" s="1">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="AW41" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX41" s="1">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AY41" s="1">
-        <v>0.78</v>
+        <v>0.54</v>
       </c>
       <c r="AZ41" s="1">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="BA41" s="1" t="s">
         <v>0</v>
@@ -30345,22 +30340,22 @@
     </row>
     <row r="42" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>632</v>
+        <v>711</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>633</v>
+        <v>712</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>634</v>
+        <v>713</v>
       </c>
       <c r="D42" s="1">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="E42" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>1375</v>
@@ -30372,34 +30367,34 @@
         <v>21</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="K42" s="1">
-        <v>1555</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>635</v>
+        <v>20</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="L42" s="1">
+        <v>462</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>148</v>
+        <v>18</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>636</v>
+        <v>715</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>637</v>
+        <v>716</v>
       </c>
       <c r="P42" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="Q42" s="1" t="s">
         <v>15</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="T42" s="1" t="s">
         <v>21</v>
@@ -30408,7 +30403,7 @@
         <v>1</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>145</v>
+        <v>41</v>
       </c>
       <c r="W42" s="1" t="s">
         <v>53</v>
@@ -30417,111 +30412,110 @@
         <v>13</v>
       </c>
       <c r="Y42" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="Z42" s="1">
-        <v>8.1670000000000006E-2</v>
+        <v>717</v>
+      </c>
+      <c r="Z42" s="1" t="s">
+        <v>718</v>
       </c>
       <c r="AA42" s="1" t="s">
         <v>11</v>
       </c>
       <c r="AB42" s="1" t="s">
-        <v>639</v>
+        <v>719</v>
       </c>
       <c r="AC42" s="1" t="s">
-        <v>639</v>
+        <v>541</v>
       </c>
       <c r="AD42" s="1" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="AE42" s="1" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="AF42" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AG42" s="1" t="s">
-        <v>640</v>
+      <c r="AG42" s="1">
+        <v>200</v>
       </c>
       <c r="AH42" s="1">
-        <v>2.0578777999999999E-2</v>
+        <f>Table1[[#This Row],[exposed_num]]/462</f>
+        <v>0.4329004329004329</v>
       </c>
       <c r="AI42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="AJ42" s="1" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="AK42" s="1" t="s">
-        <v>641</v>
+        <v>721</v>
       </c>
       <c r="AL42" s="1"/>
       <c r="AM42" s="1"/>
       <c r="AN42" s="1"/>
       <c r="AO42" s="1"/>
-      <c r="AP42" s="1"/>
-      <c r="AQ42" s="1"/>
+      <c r="AP42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ42" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="AR42" s="1" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="AS42" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AT42" s="1">
-        <v>0.74</v>
+        <v>1.27</v>
       </c>
       <c r="AU42" s="1">
-        <v>0.21</v>
+        <v>0.78</v>
       </c>
       <c r="AV42" s="1">
-        <v>2.62</v>
+        <v>2.06</v>
       </c>
       <c r="AW42" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX42" s="1">
-        <v>1.167130144605117</v>
+        <v>1.27</v>
       </c>
       <c r="AY42" s="1">
-        <v>0.35</v>
+        <v>0.78</v>
       </c>
       <c r="AZ42" s="1">
-        <v>3.89</v>
+        <v>2.06</v>
       </c>
       <c r="BA42" s="1" t="s">
-        <v>642</v>
+        <v>0</v>
       </c>
       <c r="BB42" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="BC42" s="1">
-        <v>0.74</v>
-      </c>
-      <c r="BD42" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="BE42" s="1">
-        <v>2.62</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BC42" s="1"/>
+      <c r="BD42" s="1"/>
+      <c r="BE42" s="1"/>
       <c r="BF42" s="1" t="s">
-        <v>643</v>
+        <v>0</v>
       </c>
       <c r="BG42" s="1" t="s">
-        <v>1458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>813</v>
+        <v>632</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>814</v>
+        <v>633</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>815</v>
+        <v>634</v>
       </c>
       <c r="D43" s="1">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="E43" s="1" t="b">
         <v>0</v>
@@ -30541,14 +30535,14 @@
       <c r="J43" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>816</v>
+      <c r="K43" s="1">
+        <v>1555</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>816</v>
+        <v>635</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>18</v>
+        <v>148</v>
       </c>
       <c r="N43" s="1" t="s">
         <v>636</v>
@@ -30563,7 +30557,7 @@
         <v>15</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>35</v>
@@ -30572,7 +30566,7 @@
         <v>21</v>
       </c>
       <c r="U43" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V43" s="1" t="s">
         <v>145</v>
@@ -30584,22 +30578,22 @@
         <v>13</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>817</v>
+        <v>638</v>
       </c>
       <c r="Z43" s="1">
-        <v>3.322E-2</v>
+        <v>8.1670000000000006E-2</v>
       </c>
       <c r="AA43" s="1" t="s">
         <v>11</v>
       </c>
       <c r="AB43" s="1" t="s">
-        <v>541</v>
+        <v>639</v>
       </c>
       <c r="AC43" s="1" t="s">
-        <v>541</v>
+        <v>639</v>
       </c>
       <c r="AD43" s="1" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="AE43" s="1" t="s">
         <v>53</v>
@@ -30607,11 +30601,11 @@
       <c r="AF43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AG43" s="1">
-        <v>29</v>
+      <c r="AG43" s="1" t="s">
+        <v>640</v>
       </c>
       <c r="AH43" s="1">
-        <v>5.0699301000000002E-2</v>
+        <v>2.0578777999999999E-2</v>
       </c>
       <c r="AI43" s="1" t="s">
         <v>26</v>
@@ -30620,7 +30614,7 @@
         <v>36</v>
       </c>
       <c r="AK43" s="1" t="s">
-        <v>818</v>
+        <v>641</v>
       </c>
       <c r="AL43" s="1"/>
       <c r="AM43" s="1"/>
@@ -30635,60 +30629,60 @@
         <v>1</v>
       </c>
       <c r="AT43" s="1">
-        <v>12.2</v>
+        <v>0.74</v>
       </c>
       <c r="AU43" s="1">
-        <v>3.2</v>
+        <v>0.21</v>
       </c>
       <c r="AV43" s="1">
-        <v>46.4</v>
+        <v>2.62</v>
       </c>
       <c r="AW43" s="1" t="s">
         <v>1</v>
       </c>
       <c r="AX43" s="1">
-        <v>10.6</v>
+        <v>1.167130144605117</v>
       </c>
       <c r="AY43" s="1">
-        <v>3.7</v>
+        <v>0.35</v>
       </c>
       <c r="AZ43" s="1">
-        <v>30.5</v>
+        <v>3.89</v>
       </c>
       <c r="BA43" s="1" t="s">
-        <v>60</v>
+        <v>642</v>
       </c>
       <c r="BB43" s="1" t="s">
         <v>1</v>
       </c>
       <c r="BC43" s="1">
-        <v>12.2</v>
+        <v>0.74</v>
       </c>
       <c r="BD43" s="1">
-        <v>3.2</v>
+        <v>0.21</v>
       </c>
       <c r="BE43" s="1">
-        <v>46.4</v>
+        <v>2.62</v>
       </c>
       <c r="BF43" s="1" t="s">
-        <v>60</v>
+        <v>643</v>
       </c>
       <c r="BG43" s="1" t="s">
-        <v>819</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="44" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>204</v>
+        <v>813</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>203</v>
+        <v>814</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>202</v>
+        <v>815</v>
       </c>
       <c r="D44" s="1">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="E44" s="1" t="b">
         <v>0</v>
@@ -30706,31 +30700,31 @@
         <v>21</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K44" s="1">
-        <v>307</v>
+        <v>386</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>816</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>201</v>
+        <v>816</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>148</v>
+        <v>18</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>200</v>
+        <v>636</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>42</v>
+        <v>637</v>
       </c>
       <c r="P44" t="s">
-        <v>1574</v>
+        <v>1577</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>35</v>
@@ -30739,31 +30733,31 @@
         <v>21</v>
       </c>
       <c r="U44" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V44" s="1" t="s">
-        <v>9</v>
+        <v>145</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="X44" s="1">
-        <v>0.74</v>
+        <v>53</v>
+      </c>
+      <c r="X44" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="Y44" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z44" s="1" t="s">
-        <v>197</v>
+        <v>817</v>
+      </c>
+      <c r="Z44" s="1">
+        <v>3.322E-2</v>
       </c>
       <c r="AA44" s="1" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>1433</v>
+        <v>541</v>
       </c>
       <c r="AC44" s="1" t="s">
-        <v>1433</v>
+        <v>541</v>
       </c>
       <c r="AD44" s="1" t="s">
         <v>41</v>
@@ -30774,11 +30768,11 @@
       <c r="AF44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AG44" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="AH44" s="1" t="s">
-        <v>195</v>
+      <c r="AG44" s="1">
+        <v>29</v>
+      </c>
+      <c r="AH44" s="1">
+        <v>5.0699301000000002E-2</v>
       </c>
       <c r="AI44" s="1" t="s">
         <v>26</v>
@@ -30787,7 +30781,7 @@
         <v>36</v>
       </c>
       <c r="AK44" s="1" t="s">
-        <v>3</v>
+        <v>818</v>
       </c>
       <c r="AL44" s="1"/>
       <c r="AM44" s="1"/>
@@ -30802,40 +30796,46 @@
         <v>1</v>
       </c>
       <c r="AT44" s="1">
-        <v>3.15</v>
+        <v>12.2</v>
       </c>
       <c r="AU44" s="1">
-        <v>1.19</v>
+        <v>3.2</v>
       </c>
       <c r="AV44" s="1">
-        <v>8.39</v>
+        <v>46.4</v>
       </c>
       <c r="AW44" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AX44" s="1"/>
-      <c r="AY44" s="1"/>
-      <c r="AZ44" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="AX44" s="1">
+        <v>10.6</v>
+      </c>
+      <c r="AY44" s="1">
+        <v>3.7</v>
+      </c>
+      <c r="AZ44" s="1">
+        <v>30.5</v>
+      </c>
       <c r="BA44" s="1" t="s">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BB44" s="1" t="s">
         <v>1</v>
       </c>
       <c r="BC44" s="1">
-        <v>3.15</v>
+        <v>12.2</v>
       </c>
       <c r="BD44" s="1">
-        <v>1.19</v>
+        <v>3.2</v>
       </c>
       <c r="BE44" s="1">
-        <v>8.34</v>
+        <v>46.4</v>
       </c>
       <c r="BF44" s="1" t="s">
-        <v>183</v>
+        <v>60</v>
       </c>
       <c r="BG44" s="1" t="s">
-        <v>0</v>
+        <v>819</v>
       </c>
     </row>
     <row r="45" spans="1:59" x14ac:dyDescent="0.25">
